--- a/data/Empire Carpet Care - Unit Renovation Tracker.xlsx
+++ b/data/Empire Carpet Care - Unit Renovation Tracker.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_6A7FEF4FD7D4AD5E6F236D575E5DCE3A97C5FF5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BCEF229-0C3A-4C32-92CD-2BE4BAEF51BC}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE4B51E-6969-4060-9C1E-FD9F8E585357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RenovationTracker" sheetId="1" r:id="rId1"/>
@@ -103,7 +108,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,10 +200,10 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,8 +506,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1000"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:M1001"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -519,7 +524,7 @@
     <col min="13" max="13" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="39.950000000000003" customHeight="1">
+    <row r="1" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,4069 +565,4073 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B2" s="2"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13" ht="21.95" customHeight="1">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="2"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-    </row>
-    <row r="4" spans="1:13" ht="27.95" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" spans="1:13" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-    </row>
-    <row r="5" spans="1:13" ht="21.95" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-    </row>
-    <row r="6" spans="1:13" ht="21.95" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="B7" s="2"/>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="2:13">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="2"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="2"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="2"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="2"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="2"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="2"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="2"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="2"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="2"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="2:13">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="2"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="2"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="2"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="2"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="2"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="2"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="2:13">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="2"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="2:13">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="2"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="2"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="2"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="2"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="2"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="2"/>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B40" s="2"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="2"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B42" s="2"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="2"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="2"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B45" s="2"/>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B46" s="2"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B47" s="2"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B48" s="2"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="2:13">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B49" s="2"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B50" s="2"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B51" s="2"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B52" s="2"/>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" spans="2:13">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B53" s="2"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B54" s="2"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B55" s="2"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B56" s="2"/>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B57" s="2"/>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B58" s="2"/>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" spans="2:13">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B59" s="2"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B60" s="2"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B61" s="2"/>
       <c r="M61" s="3"/>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B62" s="2"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B63" s="2"/>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B64" s="2"/>
       <c r="M64" s="3"/>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B65" s="2"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" spans="2:13">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B66" s="2"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B67" s="2"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" s="2"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" s="2"/>
       <c r="M69" s="3"/>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B70" s="2"/>
       <c r="M70" s="3"/>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B71" s="2"/>
       <c r="M71" s="3"/>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B72" s="2"/>
       <c r="M72" s="3"/>
     </row>
-    <row r="73" spans="2:13">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B73" s="2"/>
       <c r="M73" s="3"/>
     </row>
-    <row r="74" spans="2:13">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B74" s="2"/>
       <c r="M74" s="3"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B75" s="2"/>
       <c r="M75" s="3"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B76" s="2"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B77" s="2"/>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B78" s="2"/>
       <c r="M78" s="3"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B79" s="2"/>
       <c r="M79" s="3"/>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B80" s="2"/>
       <c r="M80" s="3"/>
     </row>
-    <row r="81" spans="2:13">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B81" s="2"/>
       <c r="M81" s="3"/>
     </row>
-    <row r="82" spans="2:13">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
       <c r="M82" s="3"/>
     </row>
-    <row r="83" spans="2:13">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B83" s="2"/>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" spans="2:13">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
       <c r="M84" s="3"/>
     </row>
-    <row r="85" spans="2:13">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B85" s="2"/>
       <c r="M85" s="3"/>
     </row>
-    <row r="86" spans="2:13">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
       <c r="M86" s="3"/>
     </row>
-    <row r="87" spans="2:13">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B87" s="2"/>
       <c r="M87" s="3"/>
     </row>
-    <row r="88" spans="2:13">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B88" s="2"/>
       <c r="M88" s="3"/>
     </row>
-    <row r="89" spans="2:13">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B89" s="2"/>
       <c r="M89" s="3"/>
     </row>
-    <row r="90" spans="2:13">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B90" s="2"/>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" spans="2:13">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B91" s="2"/>
       <c r="M91" s="3"/>
     </row>
-    <row r="92" spans="2:13">
+    <row r="92" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B92" s="2"/>
       <c r="M92" s="3"/>
     </row>
-    <row r="93" spans="2:13">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B93" s="2"/>
       <c r="M93" s="3"/>
     </row>
-    <row r="94" spans="2:13">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B94" s="2"/>
       <c r="M94" s="3"/>
     </row>
-    <row r="95" spans="2:13">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B95" s="2"/>
       <c r="M95" s="3"/>
     </row>
-    <row r="96" spans="2:13">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B96" s="2"/>
       <c r="M96" s="3"/>
     </row>
-    <row r="97" spans="2:13">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B97" s="2"/>
       <c r="M97" s="3"/>
     </row>
-    <row r="98" spans="2:13">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B98" s="2"/>
       <c r="M98" s="3"/>
     </row>
-    <row r="99" spans="2:13">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B99" s="2"/>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" spans="2:13">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B100" s="2"/>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" spans="2:13">
+    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B101" s="2"/>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" spans="2:13">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B102" s="2"/>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" spans="2:13">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B103" s="2"/>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" spans="2:13">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B104" s="2"/>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" spans="2:13">
+    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B105" s="2"/>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" spans="2:13">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B106" s="2"/>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" spans="2:13">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B107" s="2"/>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" spans="2:13">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B108" s="2"/>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" spans="2:13">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B109" s="2"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" spans="2:13">
+    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B110" s="2"/>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" spans="2:13">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B111" s="2"/>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" spans="2:13">
+    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B112" s="2"/>
       <c r="M112" s="3"/>
     </row>
-    <row r="113" spans="2:13">
+    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B113" s="2"/>
       <c r="M113" s="3"/>
     </row>
-    <row r="114" spans="2:13">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B114" s="2"/>
       <c r="M114" s="3"/>
     </row>
-    <row r="115" spans="2:13">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B115" s="2"/>
       <c r="M115" s="3"/>
     </row>
-    <row r="116" spans="2:13">
+    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B116" s="2"/>
       <c r="M116" s="3"/>
     </row>
-    <row r="117" spans="2:13">
+    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B117" s="2"/>
       <c r="M117" s="3"/>
     </row>
-    <row r="118" spans="2:13">
+    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B118" s="2"/>
       <c r="M118" s="3"/>
     </row>
-    <row r="119" spans="2:13">
+    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B119" s="2"/>
       <c r="M119" s="3"/>
     </row>
-    <row r="120" spans="2:13">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B120" s="2"/>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" spans="2:13">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B121" s="2"/>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" spans="2:13">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B122" s="2"/>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" spans="2:13">
+    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B123" s="2"/>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" spans="2:13">
+    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B124" s="2"/>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" spans="2:13">
+    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B125" s="2"/>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" spans="2:13">
+    <row r="126" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B126" s="2"/>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" spans="2:13">
+    <row r="127" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B127" s="2"/>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" spans="2:13">
+    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B128" s="2"/>
       <c r="M128" s="3"/>
     </row>
-    <row r="129" spans="2:13">
+    <row r="129" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B129" s="2"/>
       <c r="M129" s="3"/>
     </row>
-    <row r="130" spans="2:13">
+    <row r="130" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B130" s="2"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="2:13">
+    <row r="131" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B131" s="2"/>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" spans="2:13">
+    <row r="132" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B132" s="2"/>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" spans="2:13">
+    <row r="133" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B133" s="2"/>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" spans="2:13">
+    <row r="134" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B134" s="2"/>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" spans="2:13">
+    <row r="135" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B135" s="2"/>
       <c r="M135" s="3"/>
     </row>
-    <row r="136" spans="2:13">
+    <row r="136" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B136" s="2"/>
       <c r="M136" s="3"/>
     </row>
-    <row r="137" spans="2:13">
+    <row r="137" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B137" s="2"/>
       <c r="M137" s="3"/>
     </row>
-    <row r="138" spans="2:13">
+    <row r="138" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B138" s="2"/>
       <c r="M138" s="3"/>
     </row>
-    <row r="139" spans="2:13">
+    <row r="139" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B139" s="2"/>
       <c r="M139" s="3"/>
     </row>
-    <row r="140" spans="2:13">
+    <row r="140" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B140" s="2"/>
       <c r="M140" s="3"/>
     </row>
-    <row r="141" spans="2:13">
+    <row r="141" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B141" s="2"/>
       <c r="M141" s="3"/>
     </row>
-    <row r="142" spans="2:13">
+    <row r="142" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B142" s="2"/>
       <c r="M142" s="3"/>
     </row>
-    <row r="143" spans="2:13">
+    <row r="143" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B143" s="2"/>
       <c r="M143" s="3"/>
     </row>
-    <row r="144" spans="2:13">
+    <row r="144" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B144" s="2"/>
       <c r="M144" s="3"/>
     </row>
-    <row r="145" spans="2:13">
+    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B145" s="2"/>
       <c r="M145" s="3"/>
     </row>
-    <row r="146" spans="2:13">
+    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B146" s="2"/>
       <c r="M146" s="3"/>
     </row>
-    <row r="147" spans="2:13">
+    <row r="147" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B147" s="2"/>
       <c r="M147" s="3"/>
     </row>
-    <row r="148" spans="2:13">
+    <row r="148" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B148" s="2"/>
       <c r="M148" s="3"/>
     </row>
-    <row r="149" spans="2:13">
+    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B149" s="2"/>
       <c r="M149" s="3"/>
     </row>
-    <row r="150" spans="2:13">
+    <row r="150" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B150" s="2"/>
       <c r="M150" s="3"/>
     </row>
-    <row r="151" spans="2:13">
+    <row r="151" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B151" s="2"/>
       <c r="M151" s="3"/>
     </row>
-    <row r="152" spans="2:13">
+    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B152" s="2"/>
       <c r="M152" s="3"/>
     </row>
-    <row r="153" spans="2:13">
+    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B153" s="2"/>
       <c r="M153" s="3"/>
     </row>
-    <row r="154" spans="2:13">
+    <row r="154" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B154" s="2"/>
       <c r="M154" s="3"/>
     </row>
-    <row r="155" spans="2:13">
+    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B155" s="2"/>
       <c r="M155" s="3"/>
     </row>
-    <row r="156" spans="2:13">
+    <row r="156" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B156" s="2"/>
       <c r="M156" s="3"/>
     </row>
-    <row r="157" spans="2:13">
+    <row r="157" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B157" s="2"/>
       <c r="M157" s="3"/>
     </row>
-    <row r="158" spans="2:13">
+    <row r="158" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B158" s="2"/>
       <c r="M158" s="3"/>
     </row>
-    <row r="159" spans="2:13">
+    <row r="159" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B159" s="2"/>
       <c r="M159" s="3"/>
     </row>
-    <row r="160" spans="2:13">
+    <row r="160" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B160" s="2"/>
       <c r="M160" s="3"/>
     </row>
-    <row r="161" spans="2:13">
+    <row r="161" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B161" s="2"/>
       <c r="M161" s="3"/>
     </row>
-    <row r="162" spans="2:13">
+    <row r="162" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B162" s="2"/>
       <c r="M162" s="3"/>
     </row>
-    <row r="163" spans="2:13">
+    <row r="163" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B163" s="2"/>
       <c r="M163" s="3"/>
     </row>
-    <row r="164" spans="2:13">
+    <row r="164" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B164" s="2"/>
       <c r="M164" s="3"/>
     </row>
-    <row r="165" spans="2:13">
+    <row r="165" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B165" s="2"/>
       <c r="M165" s="3"/>
     </row>
-    <row r="166" spans="2:13">
+    <row r="166" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B166" s="2"/>
       <c r="M166" s="3"/>
     </row>
-    <row r="167" spans="2:13">
+    <row r="167" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B167" s="2"/>
       <c r="M167" s="3"/>
     </row>
-    <row r="168" spans="2:13">
+    <row r="168" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B168" s="2"/>
       <c r="M168" s="3"/>
     </row>
-    <row r="169" spans="2:13">
+    <row r="169" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B169" s="2"/>
       <c r="M169" s="3"/>
     </row>
-    <row r="170" spans="2:13">
+    <row r="170" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B170" s="2"/>
       <c r="M170" s="3"/>
     </row>
-    <row r="171" spans="2:13">
+    <row r="171" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B171" s="2"/>
       <c r="M171" s="3"/>
     </row>
-    <row r="172" spans="2:13">
+    <row r="172" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B172" s="2"/>
       <c r="M172" s="3"/>
     </row>
-    <row r="173" spans="2:13">
+    <row r="173" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B173" s="2"/>
       <c r="M173" s="3"/>
     </row>
-    <row r="174" spans="2:13">
+    <row r="174" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B174" s="2"/>
       <c r="M174" s="3"/>
     </row>
-    <row r="175" spans="2:13">
+    <row r="175" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B175" s="2"/>
       <c r="M175" s="3"/>
     </row>
-    <row r="176" spans="2:13">
+    <row r="176" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B176" s="2"/>
       <c r="M176" s="3"/>
     </row>
-    <row r="177" spans="2:13">
+    <row r="177" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B177" s="2"/>
       <c r="M177" s="3"/>
     </row>
-    <row r="178" spans="2:13">
+    <row r="178" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B178" s="2"/>
       <c r="M178" s="3"/>
     </row>
-    <row r="179" spans="2:13">
+    <row r="179" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B179" s="2"/>
       <c r="M179" s="3"/>
     </row>
-    <row r="180" spans="2:13">
+    <row r="180" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B180" s="2"/>
       <c r="M180" s="3"/>
     </row>
-    <row r="181" spans="2:13">
+    <row r="181" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B181" s="2"/>
       <c r="M181" s="3"/>
     </row>
-    <row r="182" spans="2:13">
+    <row r="182" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B182" s="2"/>
       <c r="M182" s="3"/>
     </row>
-    <row r="183" spans="2:13">
+    <row r="183" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B183" s="2"/>
       <c r="M183" s="3"/>
     </row>
-    <row r="184" spans="2:13">
+    <row r="184" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B184" s="2"/>
       <c r="M184" s="3"/>
     </row>
-    <row r="185" spans="2:13">
+    <row r="185" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B185" s="2"/>
       <c r="M185" s="3"/>
     </row>
-    <row r="186" spans="2:13">
+    <row r="186" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B186" s="2"/>
       <c r="M186" s="3"/>
     </row>
-    <row r="187" spans="2:13">
+    <row r="187" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B187" s="2"/>
       <c r="M187" s="3"/>
     </row>
-    <row r="188" spans="2:13">
+    <row r="188" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B188" s="2"/>
       <c r="M188" s="3"/>
     </row>
-    <row r="189" spans="2:13">
+    <row r="189" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B189" s="2"/>
       <c r="M189" s="3"/>
     </row>
-    <row r="190" spans="2:13">
+    <row r="190" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B190" s="2"/>
       <c r="M190" s="3"/>
     </row>
-    <row r="191" spans="2:13">
+    <row r="191" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B191" s="2"/>
       <c r="M191" s="3"/>
     </row>
-    <row r="192" spans="2:13">
+    <row r="192" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B192" s="2"/>
       <c r="M192" s="3"/>
     </row>
-    <row r="193" spans="2:13">
+    <row r="193" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B193" s="2"/>
       <c r="M193" s="3"/>
     </row>
-    <row r="194" spans="2:13">
+    <row r="194" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B194" s="2"/>
       <c r="M194" s="3"/>
     </row>
-    <row r="195" spans="2:13">
+    <row r="195" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B195" s="2"/>
       <c r="M195" s="3"/>
     </row>
-    <row r="196" spans="2:13">
+    <row r="196" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B196" s="2"/>
       <c r="M196" s="3"/>
     </row>
-    <row r="197" spans="2:13">
+    <row r="197" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B197" s="2"/>
       <c r="M197" s="3"/>
     </row>
-    <row r="198" spans="2:13">
+    <row r="198" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B198" s="2"/>
       <c r="M198" s="3"/>
     </row>
-    <row r="199" spans="2:13">
+    <row r="199" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B199" s="2"/>
       <c r="M199" s="3"/>
     </row>
-    <row r="200" spans="2:13">
+    <row r="200" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B200" s="2"/>
       <c r="M200" s="3"/>
     </row>
-    <row r="201" spans="2:13">
+    <row r="201" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B201" s="2"/>
       <c r="M201" s="3"/>
     </row>
-    <row r="202" spans="2:13">
+    <row r="202" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B202" s="2"/>
       <c r="M202" s="3"/>
     </row>
-    <row r="203" spans="2:13">
+    <row r="203" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B203" s="2"/>
       <c r="M203" s="3"/>
     </row>
-    <row r="204" spans="2:13">
+    <row r="204" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B204" s="2"/>
       <c r="M204" s="3"/>
     </row>
-    <row r="205" spans="2:13">
+    <row r="205" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B205" s="2"/>
       <c r="M205" s="3"/>
     </row>
-    <row r="206" spans="2:13">
+    <row r="206" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B206" s="2"/>
       <c r="M206" s="3"/>
     </row>
-    <row r="207" spans="2:13">
+    <row r="207" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B207" s="2"/>
       <c r="M207" s="3"/>
     </row>
-    <row r="208" spans="2:13">
+    <row r="208" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B208" s="2"/>
       <c r="M208" s="3"/>
     </row>
-    <row r="209" spans="2:13">
+    <row r="209" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B209" s="2"/>
       <c r="M209" s="3"/>
     </row>
-    <row r="210" spans="2:13">
+    <row r="210" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B210" s="2"/>
       <c r="M210" s="3"/>
     </row>
-    <row r="211" spans="2:13">
+    <row r="211" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B211" s="2"/>
       <c r="M211" s="3"/>
     </row>
-    <row r="212" spans="2:13">
+    <row r="212" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B212" s="2"/>
       <c r="M212" s="3"/>
     </row>
-    <row r="213" spans="2:13">
+    <row r="213" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B213" s="2"/>
       <c r="M213" s="3"/>
     </row>
-    <row r="214" spans="2:13">
+    <row r="214" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B214" s="2"/>
       <c r="M214" s="3"/>
     </row>
-    <row r="215" spans="2:13">
+    <row r="215" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B215" s="2"/>
       <c r="M215" s="3"/>
     </row>
-    <row r="216" spans="2:13">
+    <row r="216" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B216" s="2"/>
       <c r="M216" s="3"/>
     </row>
-    <row r="217" spans="2:13">
+    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B217" s="2"/>
       <c r="M217" s="3"/>
     </row>
-    <row r="218" spans="2:13">
+    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B218" s="2"/>
       <c r="M218" s="3"/>
     </row>
-    <row r="219" spans="2:13">
+    <row r="219" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B219" s="2"/>
       <c r="M219" s="3"/>
     </row>
-    <row r="220" spans="2:13">
+    <row r="220" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B220" s="2"/>
       <c r="M220" s="3"/>
     </row>
-    <row r="221" spans="2:13">
+    <row r="221" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B221" s="2"/>
       <c r="M221" s="3"/>
     </row>
-    <row r="222" spans="2:13">
+    <row r="222" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B222" s="2"/>
       <c r="M222" s="3"/>
     </row>
-    <row r="223" spans="2:13">
+    <row r="223" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B223" s="2"/>
       <c r="M223" s="3"/>
     </row>
-    <row r="224" spans="2:13">
+    <row r="224" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B224" s="2"/>
       <c r="M224" s="3"/>
     </row>
-    <row r="225" spans="2:13">
+    <row r="225" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B225" s="2"/>
       <c r="M225" s="3"/>
     </row>
-    <row r="226" spans="2:13">
+    <row r="226" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B226" s="2"/>
       <c r="M226" s="3"/>
     </row>
-    <row r="227" spans="2:13">
+    <row r="227" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B227" s="2"/>
       <c r="M227" s="3"/>
     </row>
-    <row r="228" spans="2:13">
+    <row r="228" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B228" s="2"/>
       <c r="M228" s="3"/>
     </row>
-    <row r="229" spans="2:13">
+    <row r="229" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B229" s="2"/>
       <c r="M229" s="3"/>
     </row>
-    <row r="230" spans="2:13">
+    <row r="230" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B230" s="2"/>
       <c r="M230" s="3"/>
     </row>
-    <row r="231" spans="2:13">
+    <row r="231" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B231" s="2"/>
       <c r="M231" s="3"/>
     </row>
-    <row r="232" spans="2:13">
+    <row r="232" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B232" s="2"/>
       <c r="M232" s="3"/>
     </row>
-    <row r="233" spans="2:13">
+    <row r="233" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B233" s="2"/>
       <c r="M233" s="3"/>
     </row>
-    <row r="234" spans="2:13">
+    <row r="234" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B234" s="2"/>
       <c r="M234" s="3"/>
     </row>
-    <row r="235" spans="2:13">
+    <row r="235" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B235" s="2"/>
       <c r="M235" s="3"/>
     </row>
-    <row r="236" spans="2:13">
+    <row r="236" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B236" s="2"/>
       <c r="M236" s="3"/>
     </row>
-    <row r="237" spans="2:13">
+    <row r="237" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B237" s="2"/>
       <c r="M237" s="3"/>
     </row>
-    <row r="238" spans="2:13">
+    <row r="238" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B238" s="2"/>
       <c r="M238" s="3"/>
     </row>
-    <row r="239" spans="2:13">
+    <row r="239" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B239" s="2"/>
       <c r="M239" s="3"/>
     </row>
-    <row r="240" spans="2:13">
+    <row r="240" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B240" s="2"/>
       <c r="M240" s="3"/>
     </row>
-    <row r="241" spans="2:13">
+    <row r="241" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B241" s="2"/>
       <c r="M241" s="3"/>
     </row>
-    <row r="242" spans="2:13">
+    <row r="242" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B242" s="2"/>
       <c r="M242" s="3"/>
     </row>
-    <row r="243" spans="2:13">
+    <row r="243" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B243" s="2"/>
       <c r="M243" s="3"/>
     </row>
-    <row r="244" spans="2:13">
+    <row r="244" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B244" s="2"/>
       <c r="M244" s="3"/>
     </row>
-    <row r="245" spans="2:13">
+    <row r="245" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B245" s="2"/>
       <c r="M245" s="3"/>
     </row>
-    <row r="246" spans="2:13">
+    <row r="246" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B246" s="2"/>
       <c r="M246" s="3"/>
     </row>
-    <row r="247" spans="2:13">
+    <row r="247" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B247" s="2"/>
       <c r="M247" s="3"/>
     </row>
-    <row r="248" spans="2:13">
+    <row r="248" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B248" s="2"/>
       <c r="M248" s="3"/>
     </row>
-    <row r="249" spans="2:13">
+    <row r="249" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B249" s="2"/>
       <c r="M249" s="3"/>
     </row>
-    <row r="250" spans="2:13">
+    <row r="250" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B250" s="2"/>
       <c r="M250" s="3"/>
     </row>
-    <row r="251" spans="2:13">
+    <row r="251" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B251" s="2"/>
       <c r="M251" s="3"/>
     </row>
-    <row r="252" spans="2:13">
+    <row r="252" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B252" s="2"/>
       <c r="M252" s="3"/>
     </row>
-    <row r="253" spans="2:13">
+    <row r="253" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B253" s="2"/>
       <c r="M253" s="3"/>
     </row>
-    <row r="254" spans="2:13">
+    <row r="254" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B254" s="2"/>
       <c r="M254" s="3"/>
     </row>
-    <row r="255" spans="2:13">
+    <row r="255" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B255" s="2"/>
       <c r="M255" s="3"/>
     </row>
-    <row r="256" spans="2:13">
+    <row r="256" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B256" s="2"/>
       <c r="M256" s="3"/>
     </row>
-    <row r="257" spans="2:13">
+    <row r="257" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B257" s="2"/>
       <c r="M257" s="3"/>
     </row>
-    <row r="258" spans="2:13">
+    <row r="258" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B258" s="2"/>
       <c r="M258" s="3"/>
     </row>
-    <row r="259" spans="2:13">
+    <row r="259" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B259" s="2"/>
       <c r="M259" s="3"/>
     </row>
-    <row r="260" spans="2:13">
+    <row r="260" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B260" s="2"/>
       <c r="M260" s="3"/>
     </row>
-    <row r="261" spans="2:13">
+    <row r="261" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B261" s="2"/>
       <c r="M261" s="3"/>
     </row>
-    <row r="262" spans="2:13">
+    <row r="262" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B262" s="2"/>
       <c r="M262" s="3"/>
     </row>
-    <row r="263" spans="2:13">
+    <row r="263" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B263" s="2"/>
       <c r="M263" s="3"/>
     </row>
-    <row r="264" spans="2:13">
+    <row r="264" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B264" s="2"/>
       <c r="M264" s="3"/>
     </row>
-    <row r="265" spans="2:13">
+    <row r="265" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B265" s="2"/>
       <c r="M265" s="3"/>
     </row>
-    <row r="266" spans="2:13">
+    <row r="266" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B266" s="2"/>
       <c r="M266" s="3"/>
     </row>
-    <row r="267" spans="2:13">
+    <row r="267" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B267" s="2"/>
       <c r="M267" s="3"/>
     </row>
-    <row r="268" spans="2:13">
+    <row r="268" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B268" s="2"/>
       <c r="M268" s="3"/>
     </row>
-    <row r="269" spans="2:13">
+    <row r="269" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B269" s="2"/>
       <c r="M269" s="3"/>
     </row>
-    <row r="270" spans="2:13">
+    <row r="270" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B270" s="2"/>
       <c r="M270" s="3"/>
     </row>
-    <row r="271" spans="2:13">
+    <row r="271" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B271" s="2"/>
       <c r="M271" s="3"/>
     </row>
-    <row r="272" spans="2:13">
+    <row r="272" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B272" s="2"/>
       <c r="M272" s="3"/>
     </row>
-    <row r="273" spans="2:13">
+    <row r="273" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B273" s="2"/>
       <c r="M273" s="3"/>
     </row>
-    <row r="274" spans="2:13">
+    <row r="274" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B274" s="2"/>
       <c r="M274" s="3"/>
     </row>
-    <row r="275" spans="2:13">
+    <row r="275" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B275" s="2"/>
       <c r="M275" s="3"/>
     </row>
-    <row r="276" spans="2:13">
+    <row r="276" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B276" s="2"/>
       <c r="M276" s="3"/>
     </row>
-    <row r="277" spans="2:13">
+    <row r="277" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B277" s="2"/>
       <c r="M277" s="3"/>
     </row>
-    <row r="278" spans="2:13">
+    <row r="278" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B278" s="2"/>
       <c r="M278" s="3"/>
     </row>
-    <row r="279" spans="2:13">
+    <row r="279" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B279" s="2"/>
       <c r="M279" s="3"/>
     </row>
-    <row r="280" spans="2:13">
+    <row r="280" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B280" s="2"/>
       <c r="M280" s="3"/>
     </row>
-    <row r="281" spans="2:13">
+    <row r="281" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B281" s="2"/>
       <c r="M281" s="3"/>
     </row>
-    <row r="282" spans="2:13">
+    <row r="282" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B282" s="2"/>
       <c r="M282" s="3"/>
     </row>
-    <row r="283" spans="2:13">
+    <row r="283" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B283" s="2"/>
       <c r="M283" s="3"/>
     </row>
-    <row r="284" spans="2:13">
+    <row r="284" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B284" s="2"/>
       <c r="M284" s="3"/>
     </row>
-    <row r="285" spans="2:13">
+    <row r="285" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B285" s="2"/>
       <c r="M285" s="3"/>
     </row>
-    <row r="286" spans="2:13">
+    <row r="286" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B286" s="2"/>
       <c r="M286" s="3"/>
     </row>
-    <row r="287" spans="2:13">
+    <row r="287" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B287" s="2"/>
       <c r="M287" s="3"/>
     </row>
-    <row r="288" spans="2:13">
+    <row r="288" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B288" s="2"/>
       <c r="M288" s="3"/>
     </row>
-    <row r="289" spans="2:13">
+    <row r="289" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B289" s="2"/>
       <c r="M289" s="3"/>
     </row>
-    <row r="290" spans="2:13">
+    <row r="290" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B290" s="2"/>
       <c r="M290" s="3"/>
     </row>
-    <row r="291" spans="2:13">
+    <row r="291" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B291" s="2"/>
       <c r="M291" s="3"/>
     </row>
-    <row r="292" spans="2:13">
+    <row r="292" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B292" s="2"/>
       <c r="M292" s="3"/>
     </row>
-    <row r="293" spans="2:13">
+    <row r="293" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B293" s="2"/>
       <c r="M293" s="3"/>
     </row>
-    <row r="294" spans="2:13">
+    <row r="294" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B294" s="2"/>
       <c r="M294" s="3"/>
     </row>
-    <row r="295" spans="2:13">
+    <row r="295" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B295" s="2"/>
       <c r="M295" s="3"/>
     </row>
-    <row r="296" spans="2:13">
+    <row r="296" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B296" s="2"/>
       <c r="M296" s="3"/>
     </row>
-    <row r="297" spans="2:13">
+    <row r="297" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B297" s="2"/>
       <c r="M297" s="3"/>
     </row>
-    <row r="298" spans="2:13">
+    <row r="298" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B298" s="2"/>
       <c r="M298" s="3"/>
     </row>
-    <row r="299" spans="2:13">
+    <row r="299" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B299" s="2"/>
       <c r="M299" s="3"/>
     </row>
-    <row r="300" spans="2:13">
+    <row r="300" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B300" s="2"/>
       <c r="M300" s="3"/>
     </row>
-    <row r="301" spans="2:13">
+    <row r="301" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B301" s="2"/>
       <c r="M301" s="3"/>
     </row>
-    <row r="302" spans="2:13">
+    <row r="302" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B302" s="2"/>
       <c r="M302" s="3"/>
     </row>
-    <row r="303" spans="2:13">
+    <row r="303" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B303" s="2"/>
       <c r="M303" s="3"/>
     </row>
-    <row r="304" spans="2:13">
+    <row r="304" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B304" s="2"/>
       <c r="M304" s="3"/>
     </row>
-    <row r="305" spans="2:13">
+    <row r="305" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B305" s="2"/>
       <c r="M305" s="3"/>
     </row>
-    <row r="306" spans="2:13">
+    <row r="306" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B306" s="2"/>
       <c r="M306" s="3"/>
     </row>
-    <row r="307" spans="2:13">
+    <row r="307" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B307" s="2"/>
       <c r="M307" s="3"/>
     </row>
-    <row r="308" spans="2:13">
+    <row r="308" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B308" s="2"/>
       <c r="M308" s="3"/>
     </row>
-    <row r="309" spans="2:13">
+    <row r="309" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B309" s="2"/>
       <c r="M309" s="3"/>
     </row>
-    <row r="310" spans="2:13">
+    <row r="310" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B310" s="2"/>
       <c r="M310" s="3"/>
     </row>
-    <row r="311" spans="2:13">
+    <row r="311" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B311" s="2"/>
       <c r="M311" s="3"/>
     </row>
-    <row r="312" spans="2:13">
+    <row r="312" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B312" s="2"/>
       <c r="M312" s="3"/>
     </row>
-    <row r="313" spans="2:13">
+    <row r="313" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B313" s="2"/>
       <c r="M313" s="3"/>
     </row>
-    <row r="314" spans="2:13">
+    <row r="314" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B314" s="2"/>
       <c r="M314" s="3"/>
     </row>
-    <row r="315" spans="2:13">
+    <row r="315" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B315" s="2"/>
       <c r="M315" s="3"/>
     </row>
-    <row r="316" spans="2:13">
+    <row r="316" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B316" s="2"/>
       <c r="M316" s="3"/>
     </row>
-    <row r="317" spans="2:13">
+    <row r="317" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B317" s="2"/>
       <c r="M317" s="3"/>
     </row>
-    <row r="318" spans="2:13">
+    <row r="318" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B318" s="2"/>
       <c r="M318" s="3"/>
     </row>
-    <row r="319" spans="2:13">
+    <row r="319" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B319" s="2"/>
       <c r="M319" s="3"/>
     </row>
-    <row r="320" spans="2:13">
+    <row r="320" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B320" s="2"/>
       <c r="M320" s="3"/>
     </row>
-    <row r="321" spans="2:13">
+    <row r="321" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B321" s="2"/>
       <c r="M321" s="3"/>
     </row>
-    <row r="322" spans="2:13">
+    <row r="322" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B322" s="2"/>
       <c r="M322" s="3"/>
     </row>
-    <row r="323" spans="2:13">
+    <row r="323" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B323" s="2"/>
       <c r="M323" s="3"/>
     </row>
-    <row r="324" spans="2:13">
+    <row r="324" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B324" s="2"/>
       <c r="M324" s="3"/>
     </row>
-    <row r="325" spans="2:13">
+    <row r="325" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B325" s="2"/>
       <c r="M325" s="3"/>
     </row>
-    <row r="326" spans="2:13">
+    <row r="326" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B326" s="2"/>
       <c r="M326" s="3"/>
     </row>
-    <row r="327" spans="2:13">
+    <row r="327" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B327" s="2"/>
       <c r="M327" s="3"/>
     </row>
-    <row r="328" spans="2:13">
+    <row r="328" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B328" s="2"/>
       <c r="M328" s="3"/>
     </row>
-    <row r="329" spans="2:13">
+    <row r="329" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B329" s="2"/>
       <c r="M329" s="3"/>
     </row>
-    <row r="330" spans="2:13">
+    <row r="330" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B330" s="2"/>
       <c r="M330" s="3"/>
     </row>
-    <row r="331" spans="2:13">
+    <row r="331" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B331" s="2"/>
       <c r="M331" s="3"/>
     </row>
-    <row r="332" spans="2:13">
+    <row r="332" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B332" s="2"/>
       <c r="M332" s="3"/>
     </row>
-    <row r="333" spans="2:13">
+    <row r="333" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B333" s="2"/>
       <c r="M333" s="3"/>
     </row>
-    <row r="334" spans="2:13">
+    <row r="334" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B334" s="2"/>
       <c r="M334" s="3"/>
     </row>
-    <row r="335" spans="2:13">
+    <row r="335" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B335" s="2"/>
       <c r="M335" s="3"/>
     </row>
-    <row r="336" spans="2:13">
+    <row r="336" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B336" s="2"/>
       <c r="M336" s="3"/>
     </row>
-    <row r="337" spans="2:13">
+    <row r="337" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B337" s="2"/>
       <c r="M337" s="3"/>
     </row>
-    <row r="338" spans="2:13">
+    <row r="338" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B338" s="2"/>
       <c r="M338" s="3"/>
     </row>
-    <row r="339" spans="2:13">
+    <row r="339" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B339" s="2"/>
       <c r="M339" s="3"/>
     </row>
-    <row r="340" spans="2:13">
+    <row r="340" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B340" s="2"/>
       <c r="M340" s="3"/>
     </row>
-    <row r="341" spans="2:13">
+    <row r="341" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B341" s="2"/>
       <c r="M341" s="3"/>
     </row>
-    <row r="342" spans="2:13">
+    <row r="342" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B342" s="2"/>
       <c r="M342" s="3"/>
     </row>
-    <row r="343" spans="2:13">
+    <row r="343" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B343" s="2"/>
       <c r="M343" s="3"/>
     </row>
-    <row r="344" spans="2:13">
+    <row r="344" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B344" s="2"/>
       <c r="M344" s="3"/>
     </row>
-    <row r="345" spans="2:13">
+    <row r="345" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B345" s="2"/>
       <c r="M345" s="3"/>
     </row>
-    <row r="346" spans="2:13">
+    <row r="346" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B346" s="2"/>
       <c r="M346" s="3"/>
     </row>
-    <row r="347" spans="2:13">
+    <row r="347" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B347" s="2"/>
       <c r="M347" s="3"/>
     </row>
-    <row r="348" spans="2:13">
+    <row r="348" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B348" s="2"/>
       <c r="M348" s="3"/>
     </row>
-    <row r="349" spans="2:13">
+    <row r="349" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B349" s="2"/>
       <c r="M349" s="3"/>
     </row>
-    <row r="350" spans="2:13">
+    <row r="350" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B350" s="2"/>
       <c r="M350" s="3"/>
     </row>
-    <row r="351" spans="2:13">
+    <row r="351" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B351" s="2"/>
       <c r="M351" s="3"/>
     </row>
-    <row r="352" spans="2:13">
+    <row r="352" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B352" s="2"/>
       <c r="M352" s="3"/>
     </row>
-    <row r="353" spans="2:13">
+    <row r="353" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B353" s="2"/>
       <c r="M353" s="3"/>
     </row>
-    <row r="354" spans="2:13">
+    <row r="354" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B354" s="2"/>
       <c r="M354" s="3"/>
     </row>
-    <row r="355" spans="2:13">
+    <row r="355" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B355" s="2"/>
       <c r="M355" s="3"/>
     </row>
-    <row r="356" spans="2:13">
+    <row r="356" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B356" s="2"/>
       <c r="M356" s="3"/>
     </row>
-    <row r="357" spans="2:13">
+    <row r="357" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B357" s="2"/>
       <c r="M357" s="3"/>
     </row>
-    <row r="358" spans="2:13">
+    <row r="358" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B358" s="2"/>
       <c r="M358" s="3"/>
     </row>
-    <row r="359" spans="2:13">
+    <row r="359" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B359" s="2"/>
       <c r="M359" s="3"/>
     </row>
-    <row r="360" spans="2:13">
+    <row r="360" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B360" s="2"/>
       <c r="M360" s="3"/>
     </row>
-    <row r="361" spans="2:13">
+    <row r="361" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B361" s="2"/>
       <c r="M361" s="3"/>
     </row>
-    <row r="362" spans="2:13">
+    <row r="362" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B362" s="2"/>
       <c r="M362" s="3"/>
     </row>
-    <row r="363" spans="2:13">
+    <row r="363" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B363" s="2"/>
       <c r="M363" s="3"/>
     </row>
-    <row r="364" spans="2:13">
+    <row r="364" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B364" s="2"/>
       <c r="M364" s="3"/>
     </row>
-    <row r="365" spans="2:13">
+    <row r="365" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B365" s="2"/>
       <c r="M365" s="3"/>
     </row>
-    <row r="366" spans="2:13">
+    <row r="366" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B366" s="2"/>
       <c r="M366" s="3"/>
     </row>
-    <row r="367" spans="2:13">
+    <row r="367" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B367" s="2"/>
       <c r="M367" s="3"/>
     </row>
-    <row r="368" spans="2:13">
+    <row r="368" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B368" s="2"/>
       <c r="M368" s="3"/>
     </row>
-    <row r="369" spans="2:13">
+    <row r="369" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B369" s="2"/>
       <c r="M369" s="3"/>
     </row>
-    <row r="370" spans="2:13">
+    <row r="370" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B370" s="2"/>
       <c r="M370" s="3"/>
     </row>
-    <row r="371" spans="2:13">
+    <row r="371" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B371" s="2"/>
       <c r="M371" s="3"/>
     </row>
-    <row r="372" spans="2:13">
+    <row r="372" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B372" s="2"/>
       <c r="M372" s="3"/>
     </row>
-    <row r="373" spans="2:13">
+    <row r="373" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B373" s="2"/>
       <c r="M373" s="3"/>
     </row>
-    <row r="374" spans="2:13">
+    <row r="374" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B374" s="2"/>
       <c r="M374" s="3"/>
     </row>
-    <row r="375" spans="2:13">
+    <row r="375" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B375" s="2"/>
       <c r="M375" s="3"/>
     </row>
-    <row r="376" spans="2:13">
+    <row r="376" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B376" s="2"/>
       <c r="M376" s="3"/>
     </row>
-    <row r="377" spans="2:13">
+    <row r="377" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B377" s="2"/>
       <c r="M377" s="3"/>
     </row>
-    <row r="378" spans="2:13">
+    <row r="378" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B378" s="2"/>
       <c r="M378" s="3"/>
     </row>
-    <row r="379" spans="2:13">
+    <row r="379" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B379" s="2"/>
       <c r="M379" s="3"/>
     </row>
-    <row r="380" spans="2:13">
+    <row r="380" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B380" s="2"/>
       <c r="M380" s="3"/>
     </row>
-    <row r="381" spans="2:13">
+    <row r="381" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B381" s="2"/>
       <c r="M381" s="3"/>
     </row>
-    <row r="382" spans="2:13">
+    <row r="382" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B382" s="2"/>
       <c r="M382" s="3"/>
     </row>
-    <row r="383" spans="2:13">
+    <row r="383" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B383" s="2"/>
       <c r="M383" s="3"/>
     </row>
-    <row r="384" spans="2:13">
+    <row r="384" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B384" s="2"/>
       <c r="M384" s="3"/>
     </row>
-    <row r="385" spans="2:13">
+    <row r="385" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B385" s="2"/>
       <c r="M385" s="3"/>
     </row>
-    <row r="386" spans="2:13">
+    <row r="386" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B386" s="2"/>
       <c r="M386" s="3"/>
     </row>
-    <row r="387" spans="2:13">
+    <row r="387" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B387" s="2"/>
       <c r="M387" s="3"/>
     </row>
-    <row r="388" spans="2:13">
+    <row r="388" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B388" s="2"/>
       <c r="M388" s="3"/>
     </row>
-    <row r="389" spans="2:13">
+    <row r="389" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B389" s="2"/>
       <c r="M389" s="3"/>
     </row>
-    <row r="390" spans="2:13">
+    <row r="390" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B390" s="2"/>
       <c r="M390" s="3"/>
     </row>
-    <row r="391" spans="2:13">
+    <row r="391" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B391" s="2"/>
       <c r="M391" s="3"/>
     </row>
-    <row r="392" spans="2:13">
+    <row r="392" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B392" s="2"/>
       <c r="M392" s="3"/>
     </row>
-    <row r="393" spans="2:13">
+    <row r="393" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B393" s="2"/>
       <c r="M393" s="3"/>
     </row>
-    <row r="394" spans="2:13">
+    <row r="394" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B394" s="2"/>
       <c r="M394" s="3"/>
     </row>
-    <row r="395" spans="2:13">
+    <row r="395" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B395" s="2"/>
       <c r="M395" s="3"/>
     </row>
-    <row r="396" spans="2:13">
+    <row r="396" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B396" s="2"/>
       <c r="M396" s="3"/>
     </row>
-    <row r="397" spans="2:13">
+    <row r="397" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B397" s="2"/>
       <c r="M397" s="3"/>
     </row>
-    <row r="398" spans="2:13">
+    <row r="398" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B398" s="2"/>
       <c r="M398" s="3"/>
     </row>
-    <row r="399" spans="2:13">
+    <row r="399" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B399" s="2"/>
       <c r="M399" s="3"/>
     </row>
-    <row r="400" spans="2:13">
+    <row r="400" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B400" s="2"/>
       <c r="M400" s="3"/>
     </row>
-    <row r="401" spans="2:13">
+    <row r="401" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B401" s="2"/>
       <c r="M401" s="3"/>
     </row>
-    <row r="402" spans="2:13">
+    <row r="402" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B402" s="2"/>
       <c r="M402" s="3"/>
     </row>
-    <row r="403" spans="2:13">
+    <row r="403" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B403" s="2"/>
       <c r="M403" s="3"/>
     </row>
-    <row r="404" spans="2:13">
+    <row r="404" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B404" s="2"/>
       <c r="M404" s="3"/>
     </row>
-    <row r="405" spans="2:13">
+    <row r="405" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B405" s="2"/>
       <c r="M405" s="3"/>
     </row>
-    <row r="406" spans="2:13">
+    <row r="406" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B406" s="2"/>
       <c r="M406" s="3"/>
     </row>
-    <row r="407" spans="2:13">
+    <row r="407" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B407" s="2"/>
       <c r="M407" s="3"/>
     </row>
-    <row r="408" spans="2:13">
+    <row r="408" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B408" s="2"/>
       <c r="M408" s="3"/>
     </row>
-    <row r="409" spans="2:13">
+    <row r="409" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B409" s="2"/>
       <c r="M409" s="3"/>
     </row>
-    <row r="410" spans="2:13">
+    <row r="410" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B410" s="2"/>
       <c r="M410" s="3"/>
     </row>
-    <row r="411" spans="2:13">
+    <row r="411" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B411" s="2"/>
       <c r="M411" s="3"/>
     </row>
-    <row r="412" spans="2:13">
+    <row r="412" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B412" s="2"/>
       <c r="M412" s="3"/>
     </row>
-    <row r="413" spans="2:13">
+    <row r="413" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B413" s="2"/>
       <c r="M413" s="3"/>
     </row>
-    <row r="414" spans="2:13">
+    <row r="414" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B414" s="2"/>
       <c r="M414" s="3"/>
     </row>
-    <row r="415" spans="2:13">
+    <row r="415" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B415" s="2"/>
       <c r="M415" s="3"/>
     </row>
-    <row r="416" spans="2:13">
+    <row r="416" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B416" s="2"/>
       <c r="M416" s="3"/>
     </row>
-    <row r="417" spans="2:13">
+    <row r="417" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B417" s="2"/>
       <c r="M417" s="3"/>
     </row>
-    <row r="418" spans="2:13">
+    <row r="418" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B418" s="2"/>
       <c r="M418" s="3"/>
     </row>
-    <row r="419" spans="2:13">
+    <row r="419" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B419" s="2"/>
       <c r="M419" s="3"/>
     </row>
-    <row r="420" spans="2:13">
+    <row r="420" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B420" s="2"/>
       <c r="M420" s="3"/>
     </row>
-    <row r="421" spans="2:13">
+    <row r="421" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B421" s="2"/>
       <c r="M421" s="3"/>
     </row>
-    <row r="422" spans="2:13">
+    <row r="422" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B422" s="2"/>
       <c r="M422" s="3"/>
     </row>
-    <row r="423" spans="2:13">
+    <row r="423" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B423" s="2"/>
       <c r="M423" s="3"/>
     </row>
-    <row r="424" spans="2:13">
+    <row r="424" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B424" s="2"/>
       <c r="M424" s="3"/>
     </row>
-    <row r="425" spans="2:13">
+    <row r="425" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B425" s="2"/>
       <c r="M425" s="3"/>
     </row>
-    <row r="426" spans="2:13">
+    <row r="426" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B426" s="2"/>
       <c r="M426" s="3"/>
     </row>
-    <row r="427" spans="2:13">
+    <row r="427" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B427" s="2"/>
       <c r="M427" s="3"/>
     </row>
-    <row r="428" spans="2:13">
+    <row r="428" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B428" s="2"/>
       <c r="M428" s="3"/>
     </row>
-    <row r="429" spans="2:13">
+    <row r="429" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B429" s="2"/>
       <c r="M429" s="3"/>
     </row>
-    <row r="430" spans="2:13">
+    <row r="430" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B430" s="2"/>
       <c r="M430" s="3"/>
     </row>
-    <row r="431" spans="2:13">
+    <row r="431" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B431" s="2"/>
       <c r="M431" s="3"/>
     </row>
-    <row r="432" spans="2:13">
+    <row r="432" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B432" s="2"/>
       <c r="M432" s="3"/>
     </row>
-    <row r="433" spans="2:13">
+    <row r="433" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B433" s="2"/>
       <c r="M433" s="3"/>
     </row>
-    <row r="434" spans="2:13">
+    <row r="434" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B434" s="2"/>
       <c r="M434" s="3"/>
     </row>
-    <row r="435" spans="2:13">
+    <row r="435" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B435" s="2"/>
       <c r="M435" s="3"/>
     </row>
-    <row r="436" spans="2:13">
+    <row r="436" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B436" s="2"/>
       <c r="M436" s="3"/>
     </row>
-    <row r="437" spans="2:13">
+    <row r="437" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B437" s="2"/>
       <c r="M437" s="3"/>
     </row>
-    <row r="438" spans="2:13">
+    <row r="438" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B438" s="2"/>
       <c r="M438" s="3"/>
     </row>
-    <row r="439" spans="2:13">
+    <row r="439" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B439" s="2"/>
       <c r="M439" s="3"/>
     </row>
-    <row r="440" spans="2:13">
+    <row r="440" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B440" s="2"/>
       <c r="M440" s="3"/>
     </row>
-    <row r="441" spans="2:13">
+    <row r="441" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B441" s="2"/>
       <c r="M441" s="3"/>
     </row>
-    <row r="442" spans="2:13">
+    <row r="442" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B442" s="2"/>
       <c r="M442" s="3"/>
     </row>
-    <row r="443" spans="2:13">
+    <row r="443" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B443" s="2"/>
       <c r="M443" s="3"/>
     </row>
-    <row r="444" spans="2:13">
+    <row r="444" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B444" s="2"/>
       <c r="M444" s="3"/>
     </row>
-    <row r="445" spans="2:13">
+    <row r="445" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B445" s="2"/>
       <c r="M445" s="3"/>
     </row>
-    <row r="446" spans="2:13">
+    <row r="446" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B446" s="2"/>
       <c r="M446" s="3"/>
     </row>
-    <row r="447" spans="2:13">
+    <row r="447" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B447" s="2"/>
       <c r="M447" s="3"/>
     </row>
-    <row r="448" spans="2:13">
+    <row r="448" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B448" s="2"/>
       <c r="M448" s="3"/>
     </row>
-    <row r="449" spans="2:13">
+    <row r="449" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B449" s="2"/>
       <c r="M449" s="3"/>
     </row>
-    <row r="450" spans="2:13">
+    <row r="450" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B450" s="2"/>
       <c r="M450" s="3"/>
     </row>
-    <row r="451" spans="2:13">
+    <row r="451" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B451" s="2"/>
       <c r="M451" s="3"/>
     </row>
-    <row r="452" spans="2:13">
+    <row r="452" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B452" s="2"/>
       <c r="M452" s="3"/>
     </row>
-    <row r="453" spans="2:13">
+    <row r="453" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B453" s="2"/>
       <c r="M453" s="3"/>
     </row>
-    <row r="454" spans="2:13">
+    <row r="454" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B454" s="2"/>
       <c r="M454" s="3"/>
     </row>
-    <row r="455" spans="2:13">
+    <row r="455" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B455" s="2"/>
       <c r="M455" s="3"/>
     </row>
-    <row r="456" spans="2:13">
+    <row r="456" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B456" s="2"/>
       <c r="M456" s="3"/>
     </row>
-    <row r="457" spans="2:13">
+    <row r="457" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B457" s="2"/>
       <c r="M457" s="3"/>
     </row>
-    <row r="458" spans="2:13">
+    <row r="458" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B458" s="2"/>
       <c r="M458" s="3"/>
     </row>
-    <row r="459" spans="2:13">
+    <row r="459" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B459" s="2"/>
       <c r="M459" s="3"/>
     </row>
-    <row r="460" spans="2:13">
+    <row r="460" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B460" s="2"/>
       <c r="M460" s="3"/>
     </row>
-    <row r="461" spans="2:13">
+    <row r="461" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B461" s="2"/>
       <c r="M461" s="3"/>
     </row>
-    <row r="462" spans="2:13">
+    <row r="462" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B462" s="2"/>
       <c r="M462" s="3"/>
     </row>
-    <row r="463" spans="2:13">
+    <row r="463" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B463" s="2"/>
       <c r="M463" s="3"/>
     </row>
-    <row r="464" spans="2:13">
+    <row r="464" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B464" s="2"/>
       <c r="M464" s="3"/>
     </row>
-    <row r="465" spans="2:13">
+    <row r="465" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B465" s="2"/>
       <c r="M465" s="3"/>
     </row>
-    <row r="466" spans="2:13">
+    <row r="466" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B466" s="2"/>
       <c r="M466" s="3"/>
     </row>
-    <row r="467" spans="2:13">
+    <row r="467" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B467" s="2"/>
       <c r="M467" s="3"/>
     </row>
-    <row r="468" spans="2:13">
+    <row r="468" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B468" s="2"/>
       <c r="M468" s="3"/>
     </row>
-    <row r="469" spans="2:13">
+    <row r="469" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B469" s="2"/>
       <c r="M469" s="3"/>
     </row>
-    <row r="470" spans="2:13">
+    <row r="470" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B470" s="2"/>
       <c r="M470" s="3"/>
     </row>
-    <row r="471" spans="2:13">
+    <row r="471" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B471" s="2"/>
       <c r="M471" s="3"/>
     </row>
-    <row r="472" spans="2:13">
+    <row r="472" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B472" s="2"/>
       <c r="M472" s="3"/>
     </row>
-    <row r="473" spans="2:13">
+    <row r="473" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B473" s="2"/>
       <c r="M473" s="3"/>
     </row>
-    <row r="474" spans="2:13">
+    <row r="474" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B474" s="2"/>
       <c r="M474" s="3"/>
     </row>
-    <row r="475" spans="2:13">
+    <row r="475" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B475" s="2"/>
       <c r="M475" s="3"/>
     </row>
-    <row r="476" spans="2:13">
+    <row r="476" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B476" s="2"/>
       <c r="M476" s="3"/>
     </row>
-    <row r="477" spans="2:13">
+    <row r="477" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B477" s="2"/>
       <c r="M477" s="3"/>
     </row>
-    <row r="478" spans="2:13">
+    <row r="478" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B478" s="2"/>
       <c r="M478" s="3"/>
     </row>
-    <row r="479" spans="2:13">
+    <row r="479" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B479" s="2"/>
       <c r="M479" s="3"/>
     </row>
-    <row r="480" spans="2:13">
+    <row r="480" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B480" s="2"/>
       <c r="M480" s="3"/>
     </row>
-    <row r="481" spans="2:13">
+    <row r="481" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B481" s="2"/>
       <c r="M481" s="3"/>
     </row>
-    <row r="482" spans="2:13">
+    <row r="482" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B482" s="2"/>
       <c r="M482" s="3"/>
     </row>
-    <row r="483" spans="2:13">
+    <row r="483" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B483" s="2"/>
       <c r="M483" s="3"/>
     </row>
-    <row r="484" spans="2:13">
+    <row r="484" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B484" s="2"/>
       <c r="M484" s="3"/>
     </row>
-    <row r="485" spans="2:13">
+    <row r="485" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B485" s="2"/>
       <c r="M485" s="3"/>
     </row>
-    <row r="486" spans="2:13">
+    <row r="486" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B486" s="2"/>
       <c r="M486" s="3"/>
     </row>
-    <row r="487" spans="2:13">
+    <row r="487" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B487" s="2"/>
       <c r="M487" s="3"/>
     </row>
-    <row r="488" spans="2:13">
+    <row r="488" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B488" s="2"/>
       <c r="M488" s="3"/>
     </row>
-    <row r="489" spans="2:13">
+    <row r="489" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B489" s="2"/>
       <c r="M489" s="3"/>
     </row>
-    <row r="490" spans="2:13">
+    <row r="490" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B490" s="2"/>
       <c r="M490" s="3"/>
     </row>
-    <row r="491" spans="2:13">
+    <row r="491" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B491" s="2"/>
       <c r="M491" s="3"/>
     </row>
-    <row r="492" spans="2:13">
+    <row r="492" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B492" s="2"/>
       <c r="M492" s="3"/>
     </row>
-    <row r="493" spans="2:13">
+    <row r="493" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B493" s="2"/>
       <c r="M493" s="3"/>
     </row>
-    <row r="494" spans="2:13">
+    <row r="494" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B494" s="2"/>
       <c r="M494" s="3"/>
     </row>
-    <row r="495" spans="2:13">
+    <row r="495" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B495" s="2"/>
       <c r="M495" s="3"/>
     </row>
-    <row r="496" spans="2:13">
+    <row r="496" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B496" s="2"/>
       <c r="M496" s="3"/>
     </row>
-    <row r="497" spans="2:13">
+    <row r="497" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B497" s="2"/>
       <c r="M497" s="3"/>
     </row>
-    <row r="498" spans="2:13">
+    <row r="498" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B498" s="2"/>
       <c r="M498" s="3"/>
     </row>
-    <row r="499" spans="2:13">
+    <row r="499" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B499" s="2"/>
       <c r="M499" s="3"/>
     </row>
-    <row r="500" spans="2:13">
+    <row r="500" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B500" s="2"/>
       <c r="M500" s="3"/>
     </row>
-    <row r="501" spans="2:13">
+    <row r="501" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B501" s="2"/>
       <c r="M501" s="3"/>
     </row>
-    <row r="502" spans="2:13">
+    <row r="502" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B502" s="2"/>
       <c r="M502" s="3"/>
     </row>
-    <row r="503" spans="2:13">
+    <row r="503" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B503" s="2"/>
       <c r="M503" s="3"/>
     </row>
-    <row r="504" spans="2:13">
+    <row r="504" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B504" s="2"/>
       <c r="M504" s="3"/>
     </row>
-    <row r="505" spans="2:13">
+    <row r="505" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B505" s="2"/>
       <c r="M505" s="3"/>
     </row>
-    <row r="506" spans="2:13">
+    <row r="506" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B506" s="2"/>
       <c r="M506" s="3"/>
     </row>
-    <row r="507" spans="2:13">
+    <row r="507" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B507" s="2"/>
       <c r="M507" s="3"/>
     </row>
-    <row r="508" spans="2:13">
+    <row r="508" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B508" s="2"/>
       <c r="M508" s="3"/>
     </row>
-    <row r="509" spans="2:13">
+    <row r="509" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B509" s="2"/>
       <c r="M509" s="3"/>
     </row>
-    <row r="510" spans="2:13">
+    <row r="510" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B510" s="2"/>
       <c r="M510" s="3"/>
     </row>
-    <row r="511" spans="2:13">
+    <row r="511" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B511" s="2"/>
       <c r="M511" s="3"/>
     </row>
-    <row r="512" spans="2:13">
+    <row r="512" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B512" s="2"/>
       <c r="M512" s="3"/>
     </row>
-    <row r="513" spans="2:13">
+    <row r="513" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B513" s="2"/>
       <c r="M513" s="3"/>
     </row>
-    <row r="514" spans="2:13">
+    <row r="514" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B514" s="2"/>
       <c r="M514" s="3"/>
     </row>
-    <row r="515" spans="2:13">
+    <row r="515" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B515" s="2"/>
       <c r="M515" s="3"/>
     </row>
-    <row r="516" spans="2:13">
+    <row r="516" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B516" s="2"/>
       <c r="M516" s="3"/>
     </row>
-    <row r="517" spans="2:13">
+    <row r="517" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B517" s="2"/>
       <c r="M517" s="3"/>
     </row>
-    <row r="518" spans="2:13">
+    <row r="518" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B518" s="2"/>
       <c r="M518" s="3"/>
     </row>
-    <row r="519" spans="2:13">
+    <row r="519" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B519" s="2"/>
       <c r="M519" s="3"/>
     </row>
-    <row r="520" spans="2:13">
+    <row r="520" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B520" s="2"/>
       <c r="M520" s="3"/>
     </row>
-    <row r="521" spans="2:13">
+    <row r="521" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B521" s="2"/>
       <c r="M521" s="3"/>
     </row>
-    <row r="522" spans="2:13">
+    <row r="522" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B522" s="2"/>
       <c r="M522" s="3"/>
     </row>
-    <row r="523" spans="2:13">
+    <row r="523" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B523" s="2"/>
       <c r="M523" s="3"/>
     </row>
-    <row r="524" spans="2:13">
+    <row r="524" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B524" s="2"/>
       <c r="M524" s="3"/>
     </row>
-    <row r="525" spans="2:13">
+    <row r="525" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B525" s="2"/>
       <c r="M525" s="3"/>
     </row>
-    <row r="526" spans="2:13">
+    <row r="526" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B526" s="2"/>
       <c r="M526" s="3"/>
     </row>
-    <row r="527" spans="2:13">
+    <row r="527" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B527" s="2"/>
       <c r="M527" s="3"/>
     </row>
-    <row r="528" spans="2:13">
+    <row r="528" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B528" s="2"/>
       <c r="M528" s="3"/>
     </row>
-    <row r="529" spans="2:13">
+    <row r="529" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B529" s="2"/>
       <c r="M529" s="3"/>
     </row>
-    <row r="530" spans="2:13">
+    <row r="530" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B530" s="2"/>
       <c r="M530" s="3"/>
     </row>
-    <row r="531" spans="2:13">
+    <row r="531" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B531" s="2"/>
       <c r="M531" s="3"/>
     </row>
-    <row r="532" spans="2:13">
+    <row r="532" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B532" s="2"/>
       <c r="M532" s="3"/>
     </row>
-    <row r="533" spans="2:13">
+    <row r="533" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B533" s="2"/>
       <c r="M533" s="3"/>
     </row>
-    <row r="534" spans="2:13">
+    <row r="534" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B534" s="2"/>
       <c r="M534" s="3"/>
     </row>
-    <row r="535" spans="2:13">
+    <row r="535" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B535" s="2"/>
       <c r="M535" s="3"/>
     </row>
-    <row r="536" spans="2:13">
+    <row r="536" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B536" s="2"/>
       <c r="M536" s="3"/>
     </row>
-    <row r="537" spans="2:13">
+    <row r="537" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B537" s="2"/>
       <c r="M537" s="3"/>
     </row>
-    <row r="538" spans="2:13">
+    <row r="538" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B538" s="2"/>
       <c r="M538" s="3"/>
     </row>
-    <row r="539" spans="2:13">
+    <row r="539" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B539" s="2"/>
       <c r="M539" s="3"/>
     </row>
-    <row r="540" spans="2:13">
+    <row r="540" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B540" s="2"/>
       <c r="M540" s="3"/>
     </row>
-    <row r="541" spans="2:13">
+    <row r="541" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B541" s="2"/>
       <c r="M541" s="3"/>
     </row>
-    <row r="542" spans="2:13">
+    <row r="542" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B542" s="2"/>
       <c r="M542" s="3"/>
     </row>
-    <row r="543" spans="2:13">
+    <row r="543" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B543" s="2"/>
       <c r="M543" s="3"/>
     </row>
-    <row r="544" spans="2:13">
+    <row r="544" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B544" s="2"/>
       <c r="M544" s="3"/>
     </row>
-    <row r="545" spans="2:13">
+    <row r="545" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B545" s="2"/>
       <c r="M545" s="3"/>
     </row>
-    <row r="546" spans="2:13">
+    <row r="546" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B546" s="2"/>
       <c r="M546" s="3"/>
     </row>
-    <row r="547" spans="2:13">
+    <row r="547" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B547" s="2"/>
       <c r="M547" s="3"/>
     </row>
-    <row r="548" spans="2:13">
+    <row r="548" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B548" s="2"/>
       <c r="M548" s="3"/>
     </row>
-    <row r="549" spans="2:13">
+    <row r="549" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B549" s="2"/>
       <c r="M549" s="3"/>
     </row>
-    <row r="550" spans="2:13">
+    <row r="550" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B550" s="2"/>
       <c r="M550" s="3"/>
     </row>
-    <row r="551" spans="2:13">
+    <row r="551" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B551" s="2"/>
       <c r="M551" s="3"/>
     </row>
-    <row r="552" spans="2:13">
+    <row r="552" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B552" s="2"/>
       <c r="M552" s="3"/>
     </row>
-    <row r="553" spans="2:13">
+    <row r="553" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B553" s="2"/>
       <c r="M553" s="3"/>
     </row>
-    <row r="554" spans="2:13">
+    <row r="554" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B554" s="2"/>
       <c r="M554" s="3"/>
     </row>
-    <row r="555" spans="2:13">
+    <row r="555" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B555" s="2"/>
       <c r="M555" s="3"/>
     </row>
-    <row r="556" spans="2:13">
+    <row r="556" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B556" s="2"/>
       <c r="M556" s="3"/>
     </row>
-    <row r="557" spans="2:13">
+    <row r="557" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B557" s="2"/>
       <c r="M557" s="3"/>
     </row>
-    <row r="558" spans="2:13">
+    <row r="558" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B558" s="2"/>
       <c r="M558" s="3"/>
     </row>
-    <row r="559" spans="2:13">
+    <row r="559" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B559" s="2"/>
       <c r="M559" s="3"/>
     </row>
-    <row r="560" spans="2:13">
+    <row r="560" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B560" s="2"/>
       <c r="M560" s="3"/>
     </row>
-    <row r="561" spans="2:13">
+    <row r="561" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B561" s="2"/>
       <c r="M561" s="3"/>
     </row>
-    <row r="562" spans="2:13">
+    <row r="562" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B562" s="2"/>
       <c r="M562" s="3"/>
     </row>
-    <row r="563" spans="2:13">
+    <row r="563" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B563" s="2"/>
       <c r="M563" s="3"/>
     </row>
-    <row r="564" spans="2:13">
+    <row r="564" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B564" s="2"/>
       <c r="M564" s="3"/>
     </row>
-    <row r="565" spans="2:13">
+    <row r="565" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B565" s="2"/>
       <c r="M565" s="3"/>
     </row>
-    <row r="566" spans="2:13">
+    <row r="566" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B566" s="2"/>
       <c r="M566" s="3"/>
     </row>
-    <row r="567" spans="2:13">
+    <row r="567" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B567" s="2"/>
       <c r="M567" s="3"/>
     </row>
-    <row r="568" spans="2:13">
+    <row r="568" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B568" s="2"/>
       <c r="M568" s="3"/>
     </row>
-    <row r="569" spans="2:13">
+    <row r="569" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B569" s="2"/>
       <c r="M569" s="3"/>
     </row>
-    <row r="570" spans="2:13">
+    <row r="570" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B570" s="2"/>
       <c r="M570" s="3"/>
     </row>
-    <row r="571" spans="2:13">
+    <row r="571" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B571" s="2"/>
       <c r="M571" s="3"/>
     </row>
-    <row r="572" spans="2:13">
+    <row r="572" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B572" s="2"/>
       <c r="M572" s="3"/>
     </row>
-    <row r="573" spans="2:13">
+    <row r="573" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B573" s="2"/>
       <c r="M573" s="3"/>
     </row>
-    <row r="574" spans="2:13">
+    <row r="574" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B574" s="2"/>
       <c r="M574" s="3"/>
     </row>
-    <row r="575" spans="2:13">
+    <row r="575" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B575" s="2"/>
       <c r="M575" s="3"/>
     </row>
-    <row r="576" spans="2:13">
+    <row r="576" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B576" s="2"/>
       <c r="M576" s="3"/>
     </row>
-    <row r="577" spans="2:13">
+    <row r="577" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B577" s="2"/>
       <c r="M577" s="3"/>
     </row>
-    <row r="578" spans="2:13">
+    <row r="578" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B578" s="2"/>
       <c r="M578" s="3"/>
     </row>
-    <row r="579" spans="2:13">
+    <row r="579" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B579" s="2"/>
       <c r="M579" s="3"/>
     </row>
-    <row r="580" spans="2:13">
+    <row r="580" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B580" s="2"/>
       <c r="M580" s="3"/>
     </row>
-    <row r="581" spans="2:13">
+    <row r="581" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B581" s="2"/>
       <c r="M581" s="3"/>
     </row>
-    <row r="582" spans="2:13">
+    <row r="582" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B582" s="2"/>
       <c r="M582" s="3"/>
     </row>
-    <row r="583" spans="2:13">
+    <row r="583" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B583" s="2"/>
       <c r="M583" s="3"/>
     </row>
-    <row r="584" spans="2:13">
+    <row r="584" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B584" s="2"/>
       <c r="M584" s="3"/>
     </row>
-    <row r="585" spans="2:13">
+    <row r="585" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B585" s="2"/>
       <c r="M585" s="3"/>
     </row>
-    <row r="586" spans="2:13">
+    <row r="586" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B586" s="2"/>
       <c r="M586" s="3"/>
     </row>
-    <row r="587" spans="2:13">
+    <row r="587" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B587" s="2"/>
       <c r="M587" s="3"/>
     </row>
-    <row r="588" spans="2:13">
+    <row r="588" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B588" s="2"/>
       <c r="M588" s="3"/>
     </row>
-    <row r="589" spans="2:13">
+    <row r="589" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B589" s="2"/>
       <c r="M589" s="3"/>
     </row>
-    <row r="590" spans="2:13">
+    <row r="590" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B590" s="2"/>
       <c r="M590" s="3"/>
     </row>
-    <row r="591" spans="2:13">
+    <row r="591" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B591" s="2"/>
       <c r="M591" s="3"/>
     </row>
-    <row r="592" spans="2:13">
+    <row r="592" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B592" s="2"/>
       <c r="M592" s="3"/>
     </row>
-    <row r="593" spans="2:13">
+    <row r="593" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B593" s="2"/>
       <c r="M593" s="3"/>
     </row>
-    <row r="594" spans="2:13">
+    <row r="594" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B594" s="2"/>
       <c r="M594" s="3"/>
     </row>
-    <row r="595" spans="2:13">
+    <row r="595" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B595" s="2"/>
       <c r="M595" s="3"/>
     </row>
-    <row r="596" spans="2:13">
+    <row r="596" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B596" s="2"/>
       <c r="M596" s="3"/>
     </row>
-    <row r="597" spans="2:13">
+    <row r="597" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B597" s="2"/>
       <c r="M597" s="3"/>
     </row>
-    <row r="598" spans="2:13">
+    <row r="598" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B598" s="2"/>
       <c r="M598" s="3"/>
     </row>
-    <row r="599" spans="2:13">
+    <row r="599" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B599" s="2"/>
       <c r="M599" s="3"/>
     </row>
-    <row r="600" spans="2:13">
+    <row r="600" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B600" s="2"/>
       <c r="M600" s="3"/>
     </row>
-    <row r="601" spans="2:13">
+    <row r="601" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B601" s="2"/>
       <c r="M601" s="3"/>
     </row>
-    <row r="602" spans="2:13">
+    <row r="602" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B602" s="2"/>
       <c r="M602" s="3"/>
     </row>
-    <row r="603" spans="2:13">
+    <row r="603" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B603" s="2"/>
       <c r="M603" s="3"/>
     </row>
-    <row r="604" spans="2:13">
+    <row r="604" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B604" s="2"/>
       <c r="M604" s="3"/>
     </row>
-    <row r="605" spans="2:13">
+    <row r="605" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B605" s="2"/>
       <c r="M605" s="3"/>
     </row>
-    <row r="606" spans="2:13">
+    <row r="606" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B606" s="2"/>
       <c r="M606" s="3"/>
     </row>
-    <row r="607" spans="2:13">
+    <row r="607" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B607" s="2"/>
       <c r="M607" s="3"/>
     </row>
-    <row r="608" spans="2:13">
+    <row r="608" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B608" s="2"/>
       <c r="M608" s="3"/>
     </row>
-    <row r="609" spans="2:13">
+    <row r="609" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B609" s="2"/>
       <c r="M609" s="3"/>
     </row>
-    <row r="610" spans="2:13">
+    <row r="610" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B610" s="2"/>
       <c r="M610" s="3"/>
     </row>
-    <row r="611" spans="2:13">
+    <row r="611" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B611" s="2"/>
       <c r="M611" s="3"/>
     </row>
-    <row r="612" spans="2:13">
+    <row r="612" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B612" s="2"/>
       <c r="M612" s="3"/>
     </row>
-    <row r="613" spans="2:13">
+    <row r="613" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B613" s="2"/>
       <c r="M613" s="3"/>
     </row>
-    <row r="614" spans="2:13">
+    <row r="614" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B614" s="2"/>
       <c r="M614" s="3"/>
     </row>
-    <row r="615" spans="2:13">
+    <row r="615" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B615" s="2"/>
       <c r="M615" s="3"/>
     </row>
-    <row r="616" spans="2:13">
+    <row r="616" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B616" s="2"/>
       <c r="M616" s="3"/>
     </row>
-    <row r="617" spans="2:13">
+    <row r="617" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B617" s="2"/>
       <c r="M617" s="3"/>
     </row>
-    <row r="618" spans="2:13">
+    <row r="618" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B618" s="2"/>
       <c r="M618" s="3"/>
     </row>
-    <row r="619" spans="2:13">
+    <row r="619" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B619" s="2"/>
       <c r="M619" s="3"/>
     </row>
-    <row r="620" spans="2:13">
+    <row r="620" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B620" s="2"/>
       <c r="M620" s="3"/>
     </row>
-    <row r="621" spans="2:13">
+    <row r="621" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B621" s="2"/>
       <c r="M621" s="3"/>
     </row>
-    <row r="622" spans="2:13">
+    <row r="622" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B622" s="2"/>
       <c r="M622" s="3"/>
     </row>
-    <row r="623" spans="2:13">
+    <row r="623" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B623" s="2"/>
       <c r="M623" s="3"/>
     </row>
-    <row r="624" spans="2:13">
+    <row r="624" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B624" s="2"/>
       <c r="M624" s="3"/>
     </row>
-    <row r="625" spans="2:13">
+    <row r="625" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B625" s="2"/>
       <c r="M625" s="3"/>
     </row>
-    <row r="626" spans="2:13">
+    <row r="626" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B626" s="2"/>
       <c r="M626" s="3"/>
     </row>
-    <row r="627" spans="2:13">
+    <row r="627" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B627" s="2"/>
       <c r="M627" s="3"/>
     </row>
-    <row r="628" spans="2:13">
+    <row r="628" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B628" s="2"/>
       <c r="M628" s="3"/>
     </row>
-    <row r="629" spans="2:13">
+    <row r="629" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B629" s="2"/>
       <c r="M629" s="3"/>
     </row>
-    <row r="630" spans="2:13">
+    <row r="630" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B630" s="2"/>
       <c r="M630" s="3"/>
     </row>
-    <row r="631" spans="2:13">
+    <row r="631" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B631" s="2"/>
       <c r="M631" s="3"/>
     </row>
-    <row r="632" spans="2:13">
+    <row r="632" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B632" s="2"/>
       <c r="M632" s="3"/>
     </row>
-    <row r="633" spans="2:13">
+    <row r="633" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B633" s="2"/>
       <c r="M633" s="3"/>
     </row>
-    <row r="634" spans="2:13">
+    <row r="634" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B634" s="2"/>
       <c r="M634" s="3"/>
     </row>
-    <row r="635" spans="2:13">
+    <row r="635" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B635" s="2"/>
       <c r="M635" s="3"/>
     </row>
-    <row r="636" spans="2:13">
+    <row r="636" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B636" s="2"/>
       <c r="M636" s="3"/>
     </row>
-    <row r="637" spans="2:13">
+    <row r="637" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B637" s="2"/>
       <c r="M637" s="3"/>
     </row>
-    <row r="638" spans="2:13">
+    <row r="638" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B638" s="2"/>
       <c r="M638" s="3"/>
     </row>
-    <row r="639" spans="2:13">
+    <row r="639" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B639" s="2"/>
       <c r="M639" s="3"/>
     </row>
-    <row r="640" spans="2:13">
+    <row r="640" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B640" s="2"/>
       <c r="M640" s="3"/>
     </row>
-    <row r="641" spans="2:13">
+    <row r="641" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B641" s="2"/>
       <c r="M641" s="3"/>
     </row>
-    <row r="642" spans="2:13">
+    <row r="642" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B642" s="2"/>
       <c r="M642" s="3"/>
     </row>
-    <row r="643" spans="2:13">
+    <row r="643" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B643" s="2"/>
       <c r="M643" s="3"/>
     </row>
-    <row r="644" spans="2:13">
+    <row r="644" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B644" s="2"/>
       <c r="M644" s="3"/>
     </row>
-    <row r="645" spans="2:13">
+    <row r="645" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B645" s="2"/>
       <c r="M645" s="3"/>
     </row>
-    <row r="646" spans="2:13">
+    <row r="646" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B646" s="2"/>
       <c r="M646" s="3"/>
     </row>
-    <row r="647" spans="2:13">
+    <row r="647" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B647" s="2"/>
       <c r="M647" s="3"/>
     </row>
-    <row r="648" spans="2:13">
+    <row r="648" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B648" s="2"/>
       <c r="M648" s="3"/>
     </row>
-    <row r="649" spans="2:13">
+    <row r="649" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B649" s="2"/>
       <c r="M649" s="3"/>
     </row>
-    <row r="650" spans="2:13">
+    <row r="650" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B650" s="2"/>
       <c r="M650" s="3"/>
     </row>
-    <row r="651" spans="2:13">
+    <row r="651" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B651" s="2"/>
       <c r="M651" s="3"/>
     </row>
-    <row r="652" spans="2:13">
+    <row r="652" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B652" s="2"/>
       <c r="M652" s="3"/>
     </row>
-    <row r="653" spans="2:13">
+    <row r="653" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B653" s="2"/>
       <c r="M653" s="3"/>
     </row>
-    <row r="654" spans="2:13">
+    <row r="654" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B654" s="2"/>
       <c r="M654" s="3"/>
     </row>
-    <row r="655" spans="2:13">
+    <row r="655" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B655" s="2"/>
       <c r="M655" s="3"/>
     </row>
-    <row r="656" spans="2:13">
+    <row r="656" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B656" s="2"/>
       <c r="M656" s="3"/>
     </row>
-    <row r="657" spans="2:13">
+    <row r="657" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B657" s="2"/>
       <c r="M657" s="3"/>
     </row>
-    <row r="658" spans="2:13">
+    <row r="658" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B658" s="2"/>
       <c r="M658" s="3"/>
     </row>
-    <row r="659" spans="2:13">
+    <row r="659" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B659" s="2"/>
       <c r="M659" s="3"/>
     </row>
-    <row r="660" spans="2:13">
+    <row r="660" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B660" s="2"/>
       <c r="M660" s="3"/>
     </row>
-    <row r="661" spans="2:13">
+    <row r="661" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B661" s="2"/>
       <c r="M661" s="3"/>
     </row>
-    <row r="662" spans="2:13">
+    <row r="662" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B662" s="2"/>
       <c r="M662" s="3"/>
     </row>
-    <row r="663" spans="2:13">
+    <row r="663" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B663" s="2"/>
       <c r="M663" s="3"/>
     </row>
-    <row r="664" spans="2:13">
+    <row r="664" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B664" s="2"/>
       <c r="M664" s="3"/>
     </row>
-    <row r="665" spans="2:13">
+    <row r="665" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B665" s="2"/>
       <c r="M665" s="3"/>
     </row>
-    <row r="666" spans="2:13">
+    <row r="666" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B666" s="2"/>
       <c r="M666" s="3"/>
     </row>
-    <row r="667" spans="2:13">
+    <row r="667" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B667" s="2"/>
       <c r="M667" s="3"/>
     </row>
-    <row r="668" spans="2:13">
+    <row r="668" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B668" s="2"/>
       <c r="M668" s="3"/>
     </row>
-    <row r="669" spans="2:13">
+    <row r="669" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B669" s="2"/>
       <c r="M669" s="3"/>
     </row>
-    <row r="670" spans="2:13">
+    <row r="670" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B670" s="2"/>
       <c r="M670" s="3"/>
     </row>
-    <row r="671" spans="2:13">
+    <row r="671" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B671" s="2"/>
       <c r="M671" s="3"/>
     </row>
-    <row r="672" spans="2:13">
+    <row r="672" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B672" s="2"/>
       <c r="M672" s="3"/>
     </row>
-    <row r="673" spans="2:13">
+    <row r="673" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B673" s="2"/>
       <c r="M673" s="3"/>
     </row>
-    <row r="674" spans="2:13">
+    <row r="674" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B674" s="2"/>
       <c r="M674" s="3"/>
     </row>
-    <row r="675" spans="2:13">
+    <row r="675" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B675" s="2"/>
       <c r="M675" s="3"/>
     </row>
-    <row r="676" spans="2:13">
+    <row r="676" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B676" s="2"/>
       <c r="M676" s="3"/>
     </row>
-    <row r="677" spans="2:13">
+    <row r="677" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B677" s="2"/>
       <c r="M677" s="3"/>
     </row>
-    <row r="678" spans="2:13">
+    <row r="678" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B678" s="2"/>
       <c r="M678" s="3"/>
     </row>
-    <row r="679" spans="2:13">
+    <row r="679" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B679" s="2"/>
       <c r="M679" s="3"/>
     </row>
-    <row r="680" spans="2:13">
+    <row r="680" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B680" s="2"/>
       <c r="M680" s="3"/>
     </row>
-    <row r="681" spans="2:13">
+    <row r="681" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B681" s="2"/>
       <c r="M681" s="3"/>
     </row>
-    <row r="682" spans="2:13">
+    <row r="682" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B682" s="2"/>
       <c r="M682" s="3"/>
     </row>
-    <row r="683" spans="2:13">
+    <row r="683" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B683" s="2"/>
       <c r="M683" s="3"/>
     </row>
-    <row r="684" spans="2:13">
+    <row r="684" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B684" s="2"/>
       <c r="M684" s="3"/>
     </row>
-    <row r="685" spans="2:13">
+    <row r="685" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B685" s="2"/>
       <c r="M685" s="3"/>
     </row>
-    <row r="686" spans="2:13">
+    <row r="686" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B686" s="2"/>
       <c r="M686" s="3"/>
     </row>
-    <row r="687" spans="2:13">
+    <row r="687" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B687" s="2"/>
       <c r="M687" s="3"/>
     </row>
-    <row r="688" spans="2:13">
+    <row r="688" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B688" s="2"/>
       <c r="M688" s="3"/>
     </row>
-    <row r="689" spans="2:13">
+    <row r="689" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B689" s="2"/>
       <c r="M689" s="3"/>
     </row>
-    <row r="690" spans="2:13">
+    <row r="690" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B690" s="2"/>
       <c r="M690" s="3"/>
     </row>
-    <row r="691" spans="2:13">
+    <row r="691" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B691" s="2"/>
       <c r="M691" s="3"/>
     </row>
-    <row r="692" spans="2:13">
+    <row r="692" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B692" s="2"/>
       <c r="M692" s="3"/>
     </row>
-    <row r="693" spans="2:13">
+    <row r="693" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B693" s="2"/>
       <c r="M693" s="3"/>
     </row>
-    <row r="694" spans="2:13">
+    <row r="694" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B694" s="2"/>
       <c r="M694" s="3"/>
     </row>
-    <row r="695" spans="2:13">
+    <row r="695" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B695" s="2"/>
       <c r="M695" s="3"/>
     </row>
-    <row r="696" spans="2:13">
+    <row r="696" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B696" s="2"/>
       <c r="M696" s="3"/>
     </row>
-    <row r="697" spans="2:13">
+    <row r="697" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B697" s="2"/>
       <c r="M697" s="3"/>
     </row>
-    <row r="698" spans="2:13">
+    <row r="698" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B698" s="2"/>
       <c r="M698" s="3"/>
     </row>
-    <row r="699" spans="2:13">
+    <row r="699" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B699" s="2"/>
       <c r="M699" s="3"/>
     </row>
-    <row r="700" spans="2:13">
+    <row r="700" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B700" s="2"/>
       <c r="M700" s="3"/>
     </row>
-    <row r="701" spans="2:13">
+    <row r="701" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B701" s="2"/>
       <c r="M701" s="3"/>
     </row>
-    <row r="702" spans="2:13">
+    <row r="702" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B702" s="2"/>
       <c r="M702" s="3"/>
     </row>
-    <row r="703" spans="2:13">
+    <row r="703" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B703" s="2"/>
       <c r="M703" s="3"/>
     </row>
-    <row r="704" spans="2:13">
+    <row r="704" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B704" s="2"/>
       <c r="M704" s="3"/>
     </row>
-    <row r="705" spans="2:13">
+    <row r="705" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B705" s="2"/>
       <c r="M705" s="3"/>
     </row>
-    <row r="706" spans="2:13">
+    <row r="706" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B706" s="2"/>
       <c r="M706" s="3"/>
     </row>
-    <row r="707" spans="2:13">
+    <row r="707" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B707" s="2"/>
       <c r="M707" s="3"/>
     </row>
-    <row r="708" spans="2:13">
+    <row r="708" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B708" s="2"/>
       <c r="M708" s="3"/>
     </row>
-    <row r="709" spans="2:13">
+    <row r="709" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B709" s="2"/>
       <c r="M709" s="3"/>
     </row>
-    <row r="710" spans="2:13">
+    <row r="710" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B710" s="2"/>
       <c r="M710" s="3"/>
     </row>
-    <row r="711" spans="2:13">
+    <row r="711" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B711" s="2"/>
       <c r="M711" s="3"/>
     </row>
-    <row r="712" spans="2:13">
+    <row r="712" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B712" s="2"/>
       <c r="M712" s="3"/>
     </row>
-    <row r="713" spans="2:13">
+    <row r="713" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B713" s="2"/>
       <c r="M713" s="3"/>
     </row>
-    <row r="714" spans="2:13">
+    <row r="714" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B714" s="2"/>
       <c r="M714" s="3"/>
     </row>
-    <row r="715" spans="2:13">
+    <row r="715" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B715" s="2"/>
       <c r="M715" s="3"/>
     </row>
-    <row r="716" spans="2:13">
+    <row r="716" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B716" s="2"/>
       <c r="M716" s="3"/>
     </row>
-    <row r="717" spans="2:13">
+    <row r="717" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B717" s="2"/>
       <c r="M717" s="3"/>
     </row>
-    <row r="718" spans="2:13">
+    <row r="718" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B718" s="2"/>
       <c r="M718" s="3"/>
     </row>
-    <row r="719" spans="2:13">
+    <row r="719" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B719" s="2"/>
       <c r="M719" s="3"/>
     </row>
-    <row r="720" spans="2:13">
+    <row r="720" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B720" s="2"/>
       <c r="M720" s="3"/>
     </row>
-    <row r="721" spans="2:13">
+    <row r="721" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B721" s="2"/>
       <c r="M721" s="3"/>
     </row>
-    <row r="722" spans="2:13">
+    <row r="722" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B722" s="2"/>
       <c r="M722" s="3"/>
     </row>
-    <row r="723" spans="2:13">
+    <row r="723" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B723" s="2"/>
       <c r="M723" s="3"/>
     </row>
-    <row r="724" spans="2:13">
+    <row r="724" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B724" s="2"/>
       <c r="M724" s="3"/>
     </row>
-    <row r="725" spans="2:13">
+    <row r="725" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B725" s="2"/>
       <c r="M725" s="3"/>
     </row>
-    <row r="726" spans="2:13">
+    <row r="726" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B726" s="2"/>
       <c r="M726" s="3"/>
     </row>
-    <row r="727" spans="2:13">
+    <row r="727" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B727" s="2"/>
       <c r="M727" s="3"/>
     </row>
-    <row r="728" spans="2:13">
+    <row r="728" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B728" s="2"/>
       <c r="M728" s="3"/>
     </row>
-    <row r="729" spans="2:13">
+    <row r="729" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B729" s="2"/>
       <c r="M729" s="3"/>
     </row>
-    <row r="730" spans="2:13">
+    <row r="730" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B730" s="2"/>
       <c r="M730" s="3"/>
     </row>
-    <row r="731" spans="2:13">
+    <row r="731" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B731" s="2"/>
       <c r="M731" s="3"/>
     </row>
-    <row r="732" spans="2:13">
+    <row r="732" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B732" s="2"/>
       <c r="M732" s="3"/>
     </row>
-    <row r="733" spans="2:13">
+    <row r="733" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B733" s="2"/>
       <c r="M733" s="3"/>
     </row>
-    <row r="734" spans="2:13">
+    <row r="734" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B734" s="2"/>
       <c r="M734" s="3"/>
     </row>
-    <row r="735" spans="2:13">
+    <row r="735" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B735" s="2"/>
       <c r="M735" s="3"/>
     </row>
-    <row r="736" spans="2:13">
+    <row r="736" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B736" s="2"/>
       <c r="M736" s="3"/>
     </row>
-    <row r="737" spans="2:13">
+    <row r="737" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B737" s="2"/>
       <c r="M737" s="3"/>
     </row>
-    <row r="738" spans="2:13">
+    <row r="738" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B738" s="2"/>
       <c r="M738" s="3"/>
     </row>
-    <row r="739" spans="2:13">
+    <row r="739" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B739" s="2"/>
       <c r="M739" s="3"/>
     </row>
-    <row r="740" spans="2:13">
+    <row r="740" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B740" s="2"/>
       <c r="M740" s="3"/>
     </row>
-    <row r="741" spans="2:13">
+    <row r="741" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B741" s="2"/>
       <c r="M741" s="3"/>
     </row>
-    <row r="742" spans="2:13">
+    <row r="742" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B742" s="2"/>
       <c r="M742" s="3"/>
     </row>
-    <row r="743" spans="2:13">
+    <row r="743" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B743" s="2"/>
       <c r="M743" s="3"/>
     </row>
-    <row r="744" spans="2:13">
+    <row r="744" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B744" s="2"/>
       <c r="M744" s="3"/>
     </row>
-    <row r="745" spans="2:13">
+    <row r="745" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B745" s="2"/>
       <c r="M745" s="3"/>
     </row>
-    <row r="746" spans="2:13">
+    <row r="746" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B746" s="2"/>
       <c r="M746" s="3"/>
     </row>
-    <row r="747" spans="2:13">
+    <row r="747" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B747" s="2"/>
       <c r="M747" s="3"/>
     </row>
-    <row r="748" spans="2:13">
+    <row r="748" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B748" s="2"/>
       <c r="M748" s="3"/>
     </row>
-    <row r="749" spans="2:13">
+    <row r="749" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B749" s="2"/>
       <c r="M749" s="3"/>
     </row>
-    <row r="750" spans="2:13">
+    <row r="750" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B750" s="2"/>
       <c r="M750" s="3"/>
     </row>
-    <row r="751" spans="2:13">
+    <row r="751" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B751" s="2"/>
       <c r="M751" s="3"/>
     </row>
-    <row r="752" spans="2:13">
+    <row r="752" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B752" s="2"/>
       <c r="M752" s="3"/>
     </row>
-    <row r="753" spans="2:13">
+    <row r="753" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B753" s="2"/>
       <c r="M753" s="3"/>
     </row>
-    <row r="754" spans="2:13">
+    <row r="754" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B754" s="2"/>
       <c r="M754" s="3"/>
     </row>
-    <row r="755" spans="2:13">
+    <row r="755" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B755" s="2"/>
       <c r="M755" s="3"/>
     </row>
-    <row r="756" spans="2:13">
+    <row r="756" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B756" s="2"/>
       <c r="M756" s="3"/>
     </row>
-    <row r="757" spans="2:13">
+    <row r="757" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B757" s="2"/>
       <c r="M757" s="3"/>
     </row>
-    <row r="758" spans="2:13">
+    <row r="758" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B758" s="2"/>
       <c r="M758" s="3"/>
     </row>
-    <row r="759" spans="2:13">
+    <row r="759" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B759" s="2"/>
       <c r="M759" s="3"/>
     </row>
-    <row r="760" spans="2:13">
+    <row r="760" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B760" s="2"/>
       <c r="M760" s="3"/>
     </row>
-    <row r="761" spans="2:13">
+    <row r="761" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B761" s="2"/>
       <c r="M761" s="3"/>
     </row>
-    <row r="762" spans="2:13">
+    <row r="762" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B762" s="2"/>
       <c r="M762" s="3"/>
     </row>
-    <row r="763" spans="2:13">
+    <row r="763" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B763" s="2"/>
       <c r="M763" s="3"/>
     </row>
-    <row r="764" spans="2:13">
+    <row r="764" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B764" s="2"/>
       <c r="M764" s="3"/>
     </row>
-    <row r="765" spans="2:13">
+    <row r="765" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B765" s="2"/>
       <c r="M765" s="3"/>
     </row>
-    <row r="766" spans="2:13">
+    <row r="766" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B766" s="2"/>
       <c r="M766" s="3"/>
     </row>
-    <row r="767" spans="2:13">
+    <row r="767" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B767" s="2"/>
       <c r="M767" s="3"/>
     </row>
-    <row r="768" spans="2:13">
+    <row r="768" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B768" s="2"/>
       <c r="M768" s="3"/>
     </row>
-    <row r="769" spans="2:13">
+    <row r="769" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B769" s="2"/>
       <c r="M769" s="3"/>
     </row>
-    <row r="770" spans="2:13">
+    <row r="770" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B770" s="2"/>
       <c r="M770" s="3"/>
     </row>
-    <row r="771" spans="2:13">
+    <row r="771" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B771" s="2"/>
       <c r="M771" s="3"/>
     </row>
-    <row r="772" spans="2:13">
+    <row r="772" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B772" s="2"/>
       <c r="M772" s="3"/>
     </row>
-    <row r="773" spans="2:13">
+    <row r="773" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B773" s="2"/>
       <c r="M773" s="3"/>
     </row>
-    <row r="774" spans="2:13">
+    <row r="774" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B774" s="2"/>
       <c r="M774" s="3"/>
     </row>
-    <row r="775" spans="2:13">
+    <row r="775" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B775" s="2"/>
       <c r="M775" s="3"/>
     </row>
-    <row r="776" spans="2:13">
+    <row r="776" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B776" s="2"/>
       <c r="M776" s="3"/>
     </row>
-    <row r="777" spans="2:13">
+    <row r="777" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B777" s="2"/>
       <c r="M777" s="3"/>
     </row>
-    <row r="778" spans="2:13">
+    <row r="778" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B778" s="2"/>
       <c r="M778" s="3"/>
     </row>
-    <row r="779" spans="2:13">
+    <row r="779" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B779" s="2"/>
       <c r="M779" s="3"/>
     </row>
-    <row r="780" spans="2:13">
+    <row r="780" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B780" s="2"/>
       <c r="M780" s="3"/>
     </row>
-    <row r="781" spans="2:13">
+    <row r="781" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B781" s="2"/>
       <c r="M781" s="3"/>
     </row>
-    <row r="782" spans="2:13">
+    <row r="782" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B782" s="2"/>
       <c r="M782" s="3"/>
     </row>
-    <row r="783" spans="2:13">
+    <row r="783" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B783" s="2"/>
       <c r="M783" s="3"/>
     </row>
-    <row r="784" spans="2:13">
+    <row r="784" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B784" s="2"/>
       <c r="M784" s="3"/>
     </row>
-    <row r="785" spans="2:13">
+    <row r="785" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B785" s="2"/>
       <c r="M785" s="3"/>
     </row>
-    <row r="786" spans="2:13">
+    <row r="786" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B786" s="2"/>
       <c r="M786" s="3"/>
     </row>
-    <row r="787" spans="2:13">
+    <row r="787" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B787" s="2"/>
       <c r="M787" s="3"/>
     </row>
-    <row r="788" spans="2:13">
+    <row r="788" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B788" s="2"/>
       <c r="M788" s="3"/>
     </row>
-    <row r="789" spans="2:13">
+    <row r="789" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B789" s="2"/>
       <c r="M789" s="3"/>
     </row>
-    <row r="790" spans="2:13">
+    <row r="790" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B790" s="2"/>
       <c r="M790" s="3"/>
     </row>
-    <row r="791" spans="2:13">
+    <row r="791" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B791" s="2"/>
       <c r="M791" s="3"/>
     </row>
-    <row r="792" spans="2:13">
+    <row r="792" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B792" s="2"/>
       <c r="M792" s="3"/>
     </row>
-    <row r="793" spans="2:13">
+    <row r="793" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B793" s="2"/>
       <c r="M793" s="3"/>
     </row>
-    <row r="794" spans="2:13">
+    <row r="794" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B794" s="2"/>
       <c r="M794" s="3"/>
     </row>
-    <row r="795" spans="2:13">
+    <row r="795" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B795" s="2"/>
       <c r="M795" s="3"/>
     </row>
-    <row r="796" spans="2:13">
+    <row r="796" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B796" s="2"/>
       <c r="M796" s="3"/>
     </row>
-    <row r="797" spans="2:13">
+    <row r="797" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B797" s="2"/>
       <c r="M797" s="3"/>
     </row>
-    <row r="798" spans="2:13">
+    <row r="798" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B798" s="2"/>
       <c r="M798" s="3"/>
     </row>
-    <row r="799" spans="2:13">
+    <row r="799" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B799" s="2"/>
       <c r="M799" s="3"/>
     </row>
-    <row r="800" spans="2:13">
+    <row r="800" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B800" s="2"/>
       <c r="M800" s="3"/>
     </row>
-    <row r="801" spans="2:13">
+    <row r="801" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B801" s="2"/>
       <c r="M801" s="3"/>
     </row>
-    <row r="802" spans="2:13">
+    <row r="802" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B802" s="2"/>
       <c r="M802" s="3"/>
     </row>
-    <row r="803" spans="2:13">
+    <row r="803" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B803" s="2"/>
       <c r="M803" s="3"/>
     </row>
-    <row r="804" spans="2:13">
+    <row r="804" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B804" s="2"/>
       <c r="M804" s="3"/>
     </row>
-    <row r="805" spans="2:13">
+    <row r="805" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B805" s="2"/>
       <c r="M805" s="3"/>
     </row>
-    <row r="806" spans="2:13">
+    <row r="806" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B806" s="2"/>
       <c r="M806" s="3"/>
     </row>
-    <row r="807" spans="2:13">
+    <row r="807" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B807" s="2"/>
       <c r="M807" s="3"/>
     </row>
-    <row r="808" spans="2:13">
+    <row r="808" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B808" s="2"/>
       <c r="M808" s="3"/>
     </row>
-    <row r="809" spans="2:13">
+    <row r="809" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B809" s="2"/>
       <c r="M809" s="3"/>
     </row>
-    <row r="810" spans="2:13">
+    <row r="810" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B810" s="2"/>
       <c r="M810" s="3"/>
     </row>
-    <row r="811" spans="2:13">
+    <row r="811" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B811" s="2"/>
       <c r="M811" s="3"/>
     </row>
-    <row r="812" spans="2:13">
+    <row r="812" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B812" s="2"/>
       <c r="M812" s="3"/>
     </row>
-    <row r="813" spans="2:13">
+    <row r="813" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B813" s="2"/>
       <c r="M813" s="3"/>
     </row>
-    <row r="814" spans="2:13">
+    <row r="814" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B814" s="2"/>
       <c r="M814" s="3"/>
     </row>
-    <row r="815" spans="2:13">
+    <row r="815" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B815" s="2"/>
       <c r="M815" s="3"/>
     </row>
-    <row r="816" spans="2:13">
+    <row r="816" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B816" s="2"/>
       <c r="M816" s="3"/>
     </row>
-    <row r="817" spans="2:13">
+    <row r="817" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B817" s="2"/>
       <c r="M817" s="3"/>
     </row>
-    <row r="818" spans="2:13">
+    <row r="818" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B818" s="2"/>
       <c r="M818" s="3"/>
     </row>
-    <row r="819" spans="2:13">
+    <row r="819" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B819" s="2"/>
       <c r="M819" s="3"/>
     </row>
-    <row r="820" spans="2:13">
+    <row r="820" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B820" s="2"/>
       <c r="M820" s="3"/>
     </row>
-    <row r="821" spans="2:13">
+    <row r="821" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B821" s="2"/>
       <c r="M821" s="3"/>
     </row>
-    <row r="822" spans="2:13">
+    <row r="822" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B822" s="2"/>
       <c r="M822" s="3"/>
     </row>
-    <row r="823" spans="2:13">
+    <row r="823" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B823" s="2"/>
       <c r="M823" s="3"/>
     </row>
-    <row r="824" spans="2:13">
+    <row r="824" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B824" s="2"/>
       <c r="M824" s="3"/>
     </row>
-    <row r="825" spans="2:13">
+    <row r="825" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B825" s="2"/>
       <c r="M825" s="3"/>
     </row>
-    <row r="826" spans="2:13">
+    <row r="826" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B826" s="2"/>
       <c r="M826" s="3"/>
     </row>
-    <row r="827" spans="2:13">
+    <row r="827" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B827" s="2"/>
       <c r="M827" s="3"/>
     </row>
-    <row r="828" spans="2:13">
+    <row r="828" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B828" s="2"/>
       <c r="M828" s="3"/>
     </row>
-    <row r="829" spans="2:13">
+    <row r="829" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B829" s="2"/>
       <c r="M829" s="3"/>
     </row>
-    <row r="830" spans="2:13">
+    <row r="830" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B830" s="2"/>
       <c r="M830" s="3"/>
     </row>
-    <row r="831" spans="2:13">
+    <row r="831" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B831" s="2"/>
       <c r="M831" s="3"/>
     </row>
-    <row r="832" spans="2:13">
+    <row r="832" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B832" s="2"/>
       <c r="M832" s="3"/>
     </row>
-    <row r="833" spans="2:13">
+    <row r="833" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B833" s="2"/>
       <c r="M833" s="3"/>
     </row>
-    <row r="834" spans="2:13">
+    <row r="834" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B834" s="2"/>
       <c r="M834" s="3"/>
     </row>
-    <row r="835" spans="2:13">
+    <row r="835" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B835" s="2"/>
       <c r="M835" s="3"/>
     </row>
-    <row r="836" spans="2:13">
+    <row r="836" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B836" s="2"/>
       <c r="M836" s="3"/>
     </row>
-    <row r="837" spans="2:13">
+    <row r="837" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B837" s="2"/>
       <c r="M837" s="3"/>
     </row>
-    <row r="838" spans="2:13">
+    <row r="838" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B838" s="2"/>
       <c r="M838" s="3"/>
     </row>
-    <row r="839" spans="2:13">
+    <row r="839" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B839" s="2"/>
       <c r="M839" s="3"/>
     </row>
-    <row r="840" spans="2:13">
+    <row r="840" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B840" s="2"/>
       <c r="M840" s="3"/>
     </row>
-    <row r="841" spans="2:13">
+    <row r="841" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B841" s="2"/>
       <c r="M841" s="3"/>
     </row>
-    <row r="842" spans="2:13">
+    <row r="842" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B842" s="2"/>
       <c r="M842" s="3"/>
     </row>
-    <row r="843" spans="2:13">
+    <row r="843" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B843" s="2"/>
       <c r="M843" s="3"/>
     </row>
-    <row r="844" spans="2:13">
+    <row r="844" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B844" s="2"/>
       <c r="M844" s="3"/>
     </row>
-    <row r="845" spans="2:13">
+    <row r="845" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B845" s="2"/>
       <c r="M845" s="3"/>
     </row>
-    <row r="846" spans="2:13">
+    <row r="846" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B846" s="2"/>
       <c r="M846" s="3"/>
     </row>
-    <row r="847" spans="2:13">
+    <row r="847" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B847" s="2"/>
       <c r="M847" s="3"/>
     </row>
-    <row r="848" spans="2:13">
+    <row r="848" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B848" s="2"/>
       <c r="M848" s="3"/>
     </row>
-    <row r="849" spans="2:13">
+    <row r="849" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B849" s="2"/>
       <c r="M849" s="3"/>
     </row>
-    <row r="850" spans="2:13">
+    <row r="850" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B850" s="2"/>
       <c r="M850" s="3"/>
     </row>
-    <row r="851" spans="2:13">
+    <row r="851" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B851" s="2"/>
       <c r="M851" s="3"/>
     </row>
-    <row r="852" spans="2:13">
+    <row r="852" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B852" s="2"/>
       <c r="M852" s="3"/>
     </row>
-    <row r="853" spans="2:13">
+    <row r="853" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B853" s="2"/>
       <c r="M853" s="3"/>
     </row>
-    <row r="854" spans="2:13">
+    <row r="854" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B854" s="2"/>
       <c r="M854" s="3"/>
     </row>
-    <row r="855" spans="2:13">
+    <row r="855" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B855" s="2"/>
       <c r="M855" s="3"/>
     </row>
-    <row r="856" spans="2:13">
+    <row r="856" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B856" s="2"/>
       <c r="M856" s="3"/>
     </row>
-    <row r="857" spans="2:13">
+    <row r="857" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B857" s="2"/>
       <c r="M857" s="3"/>
     </row>
-    <row r="858" spans="2:13">
+    <row r="858" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B858" s="2"/>
       <c r="M858" s="3"/>
     </row>
-    <row r="859" spans="2:13">
+    <row r="859" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B859" s="2"/>
       <c r="M859" s="3"/>
     </row>
-    <row r="860" spans="2:13">
+    <row r="860" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B860" s="2"/>
       <c r="M860" s="3"/>
     </row>
-    <row r="861" spans="2:13">
+    <row r="861" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B861" s="2"/>
       <c r="M861" s="3"/>
     </row>
-    <row r="862" spans="2:13">
+    <row r="862" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B862" s="2"/>
       <c r="M862" s="3"/>
     </row>
-    <row r="863" spans="2:13">
+    <row r="863" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B863" s="2"/>
       <c r="M863" s="3"/>
     </row>
-    <row r="864" spans="2:13">
+    <row r="864" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B864" s="2"/>
       <c r="M864" s="3"/>
     </row>
-    <row r="865" spans="2:13">
+    <row r="865" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B865" s="2"/>
       <c r="M865" s="3"/>
     </row>
-    <row r="866" spans="2:13">
+    <row r="866" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B866" s="2"/>
       <c r="M866" s="3"/>
     </row>
-    <row r="867" spans="2:13">
+    <row r="867" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B867" s="2"/>
       <c r="M867" s="3"/>
     </row>
-    <row r="868" spans="2:13">
+    <row r="868" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B868" s="2"/>
       <c r="M868" s="3"/>
     </row>
-    <row r="869" spans="2:13">
+    <row r="869" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B869" s="2"/>
       <c r="M869" s="3"/>
     </row>
-    <row r="870" spans="2:13">
+    <row r="870" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B870" s="2"/>
       <c r="M870" s="3"/>
     </row>
-    <row r="871" spans="2:13">
+    <row r="871" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B871" s="2"/>
       <c r="M871" s="3"/>
     </row>
-    <row r="872" spans="2:13">
+    <row r="872" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B872" s="2"/>
       <c r="M872" s="3"/>
     </row>
-    <row r="873" spans="2:13">
+    <row r="873" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B873" s="2"/>
       <c r="M873" s="3"/>
     </row>
-    <row r="874" spans="2:13">
+    <row r="874" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B874" s="2"/>
       <c r="M874" s="3"/>
     </row>
-    <row r="875" spans="2:13">
+    <row r="875" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B875" s="2"/>
       <c r="M875" s="3"/>
     </row>
-    <row r="876" spans="2:13">
+    <row r="876" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B876" s="2"/>
       <c r="M876" s="3"/>
     </row>
-    <row r="877" spans="2:13">
+    <row r="877" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B877" s="2"/>
       <c r="M877" s="3"/>
     </row>
-    <row r="878" spans="2:13">
+    <row r="878" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B878" s="2"/>
       <c r="M878" s="3"/>
     </row>
-    <row r="879" spans="2:13">
+    <row r="879" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B879" s="2"/>
       <c r="M879" s="3"/>
     </row>
-    <row r="880" spans="2:13">
+    <row r="880" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B880" s="2"/>
       <c r="M880" s="3"/>
     </row>
-    <row r="881" spans="2:13">
+    <row r="881" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B881" s="2"/>
       <c r="M881" s="3"/>
     </row>
-    <row r="882" spans="2:13">
+    <row r="882" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B882" s="2"/>
       <c r="M882" s="3"/>
     </row>
-    <row r="883" spans="2:13">
+    <row r="883" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B883" s="2"/>
       <c r="M883" s="3"/>
     </row>
-    <row r="884" spans="2:13">
+    <row r="884" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B884" s="2"/>
       <c r="M884" s="3"/>
     </row>
-    <row r="885" spans="2:13">
+    <row r="885" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B885" s="2"/>
       <c r="M885" s="3"/>
     </row>
-    <row r="886" spans="2:13">
+    <row r="886" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B886" s="2"/>
       <c r="M886" s="3"/>
     </row>
-    <row r="887" spans="2:13">
+    <row r="887" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B887" s="2"/>
       <c r="M887" s="3"/>
     </row>
-    <row r="888" spans="2:13">
+    <row r="888" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B888" s="2"/>
       <c r="M888" s="3"/>
     </row>
-    <row r="889" spans="2:13">
+    <row r="889" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B889" s="2"/>
       <c r="M889" s="3"/>
     </row>
-    <row r="890" spans="2:13">
+    <row r="890" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B890" s="2"/>
       <c r="M890" s="3"/>
     </row>
-    <row r="891" spans="2:13">
+    <row r="891" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B891" s="2"/>
       <c r="M891" s="3"/>
     </row>
-    <row r="892" spans="2:13">
+    <row r="892" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B892" s="2"/>
       <c r="M892" s="3"/>
     </row>
-    <row r="893" spans="2:13">
+    <row r="893" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B893" s="2"/>
       <c r="M893" s="3"/>
     </row>
-    <row r="894" spans="2:13">
+    <row r="894" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B894" s="2"/>
       <c r="M894" s="3"/>
     </row>
-    <row r="895" spans="2:13">
+    <row r="895" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B895" s="2"/>
       <c r="M895" s="3"/>
     </row>
-    <row r="896" spans="2:13">
+    <row r="896" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B896" s="2"/>
       <c r="M896" s="3"/>
     </row>
-    <row r="897" spans="2:13">
+    <row r="897" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B897" s="2"/>
       <c r="M897" s="3"/>
     </row>
-    <row r="898" spans="2:13">
+    <row r="898" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B898" s="2"/>
       <c r="M898" s="3"/>
     </row>
-    <row r="899" spans="2:13">
+    <row r="899" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B899" s="2"/>
       <c r="M899" s="3"/>
     </row>
-    <row r="900" spans="2:13">
+    <row r="900" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B900" s="2"/>
       <c r="M900" s="3"/>
     </row>
-    <row r="901" spans="2:13">
+    <row r="901" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B901" s="2"/>
       <c r="M901" s="3"/>
     </row>
-    <row r="902" spans="2:13">
+    <row r="902" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B902" s="2"/>
       <c r="M902" s="3"/>
     </row>
-    <row r="903" spans="2:13">
+    <row r="903" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B903" s="2"/>
       <c r="M903" s="3"/>
     </row>
-    <row r="904" spans="2:13">
+    <row r="904" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B904" s="2"/>
       <c r="M904" s="3"/>
     </row>
-    <row r="905" spans="2:13">
+    <row r="905" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B905" s="2"/>
       <c r="M905" s="3"/>
     </row>
-    <row r="906" spans="2:13">
+    <row r="906" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B906" s="2"/>
       <c r="M906" s="3"/>
     </row>
-    <row r="907" spans="2:13">
+    <row r="907" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B907" s="2"/>
       <c r="M907" s="3"/>
     </row>
-    <row r="908" spans="2:13">
+    <row r="908" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B908" s="2"/>
       <c r="M908" s="3"/>
     </row>
-    <row r="909" spans="2:13">
+    <row r="909" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B909" s="2"/>
       <c r="M909" s="3"/>
     </row>
-    <row r="910" spans="2:13">
+    <row r="910" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B910" s="2"/>
       <c r="M910" s="3"/>
     </row>
-    <row r="911" spans="2:13">
+    <row r="911" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B911" s="2"/>
       <c r="M911" s="3"/>
     </row>
-    <row r="912" spans="2:13">
+    <row r="912" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B912" s="2"/>
       <c r="M912" s="3"/>
     </row>
-    <row r="913" spans="2:13">
+    <row r="913" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B913" s="2"/>
       <c r="M913" s="3"/>
     </row>
-    <row r="914" spans="2:13">
+    <row r="914" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B914" s="2"/>
       <c r="M914" s="3"/>
     </row>
-    <row r="915" spans="2:13">
+    <row r="915" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B915" s="2"/>
       <c r="M915" s="3"/>
     </row>
-    <row r="916" spans="2:13">
+    <row r="916" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B916" s="2"/>
       <c r="M916" s="3"/>
     </row>
-    <row r="917" spans="2:13">
+    <row r="917" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B917" s="2"/>
       <c r="M917" s="3"/>
     </row>
-    <row r="918" spans="2:13">
+    <row r="918" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B918" s="2"/>
       <c r="M918" s="3"/>
     </row>
-    <row r="919" spans="2:13">
+    <row r="919" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B919" s="2"/>
       <c r="M919" s="3"/>
     </row>
-    <row r="920" spans="2:13">
+    <row r="920" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B920" s="2"/>
       <c r="M920" s="3"/>
     </row>
-    <row r="921" spans="2:13">
+    <row r="921" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B921" s="2"/>
       <c r="M921" s="3"/>
     </row>
-    <row r="922" spans="2:13">
+    <row r="922" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B922" s="2"/>
       <c r="M922" s="3"/>
     </row>
-    <row r="923" spans="2:13">
+    <row r="923" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B923" s="2"/>
       <c r="M923" s="3"/>
     </row>
-    <row r="924" spans="2:13">
+    <row r="924" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B924" s="2"/>
       <c r="M924" s="3"/>
     </row>
-    <row r="925" spans="2:13">
+    <row r="925" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B925" s="2"/>
       <c r="M925" s="3"/>
     </row>
-    <row r="926" spans="2:13">
+    <row r="926" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B926" s="2"/>
       <c r="M926" s="3"/>
     </row>
-    <row r="927" spans="2:13">
+    <row r="927" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B927" s="2"/>
       <c r="M927" s="3"/>
     </row>
-    <row r="928" spans="2:13">
+    <row r="928" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B928" s="2"/>
       <c r="M928" s="3"/>
     </row>
-    <row r="929" spans="2:13">
+    <row r="929" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B929" s="2"/>
       <c r="M929" s="3"/>
     </row>
-    <row r="930" spans="2:13">
+    <row r="930" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B930" s="2"/>
       <c r="M930" s="3"/>
     </row>
-    <row r="931" spans="2:13">
+    <row r="931" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B931" s="2"/>
       <c r="M931" s="3"/>
     </row>
-    <row r="932" spans="2:13">
+    <row r="932" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B932" s="2"/>
       <c r="M932" s="3"/>
     </row>
-    <row r="933" spans="2:13">
+    <row r="933" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B933" s="2"/>
       <c r="M933" s="3"/>
     </row>
-    <row r="934" spans="2:13">
+    <row r="934" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B934" s="2"/>
       <c r="M934" s="3"/>
     </row>
-    <row r="935" spans="2:13">
+    <row r="935" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B935" s="2"/>
       <c r="M935" s="3"/>
     </row>
-    <row r="936" spans="2:13">
+    <row r="936" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B936" s="2"/>
       <c r="M936" s="3"/>
     </row>
-    <row r="937" spans="2:13">
+    <row r="937" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B937" s="2"/>
       <c r="M937" s="3"/>
     </row>
-    <row r="938" spans="2:13">
+    <row r="938" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B938" s="2"/>
       <c r="M938" s="3"/>
     </row>
-    <row r="939" spans="2:13">
+    <row r="939" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B939" s="2"/>
       <c r="M939" s="3"/>
     </row>
-    <row r="940" spans="2:13">
+    <row r="940" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B940" s="2"/>
       <c r="M940" s="3"/>
     </row>
-    <row r="941" spans="2:13">
+    <row r="941" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B941" s="2"/>
       <c r="M941" s="3"/>
     </row>
-    <row r="942" spans="2:13">
+    <row r="942" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B942" s="2"/>
       <c r="M942" s="3"/>
     </row>
-    <row r="943" spans="2:13">
+    <row r="943" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B943" s="2"/>
       <c r="M943" s="3"/>
     </row>
-    <row r="944" spans="2:13">
+    <row r="944" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B944" s="2"/>
       <c r="M944" s="3"/>
     </row>
-    <row r="945" spans="2:13">
+    <row r="945" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B945" s="2"/>
       <c r="M945" s="3"/>
     </row>
-    <row r="946" spans="2:13">
+    <row r="946" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B946" s="2"/>
       <c r="M946" s="3"/>
     </row>
-    <row r="947" spans="2:13">
+    <row r="947" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B947" s="2"/>
       <c r="M947" s="3"/>
     </row>
-    <row r="948" spans="2:13">
+    <row r="948" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B948" s="2"/>
       <c r="M948" s="3"/>
     </row>
-    <row r="949" spans="2:13">
+    <row r="949" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B949" s="2"/>
       <c r="M949" s="3"/>
     </row>
-    <row r="950" spans="2:13">
+    <row r="950" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B950" s="2"/>
       <c r="M950" s="3"/>
     </row>
-    <row r="951" spans="2:13">
+    <row r="951" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B951" s="2"/>
       <c r="M951" s="3"/>
     </row>
-    <row r="952" spans="2:13">
+    <row r="952" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B952" s="2"/>
       <c r="M952" s="3"/>
     </row>
-    <row r="953" spans="2:13">
+    <row r="953" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B953" s="2"/>
       <c r="M953" s="3"/>
     </row>
-    <row r="954" spans="2:13">
+    <row r="954" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B954" s="2"/>
       <c r="M954" s="3"/>
     </row>
-    <row r="955" spans="2:13">
+    <row r="955" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B955" s="2"/>
       <c r="M955" s="3"/>
     </row>
-    <row r="956" spans="2:13">
+    <row r="956" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B956" s="2"/>
       <c r="M956" s="3"/>
     </row>
-    <row r="957" spans="2:13">
+    <row r="957" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B957" s="2"/>
       <c r="M957" s="3"/>
     </row>
-    <row r="958" spans="2:13">
+    <row r="958" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B958" s="2"/>
       <c r="M958" s="3"/>
     </row>
-    <row r="959" spans="2:13">
+    <row r="959" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B959" s="2"/>
       <c r="M959" s="3"/>
     </row>
-    <row r="960" spans="2:13">
+    <row r="960" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B960" s="2"/>
       <c r="M960" s="3"/>
     </row>
-    <row r="961" spans="2:13">
+    <row r="961" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B961" s="2"/>
       <c r="M961" s="3"/>
     </row>
-    <row r="962" spans="2:13">
+    <row r="962" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B962" s="2"/>
       <c r="M962" s="3"/>
     </row>
-    <row r="963" spans="2:13">
+    <row r="963" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B963" s="2"/>
       <c r="M963" s="3"/>
     </row>
-    <row r="964" spans="2:13">
+    <row r="964" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B964" s="2"/>
       <c r="M964" s="3"/>
     </row>
-    <row r="965" spans="2:13">
+    <row r="965" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B965" s="2"/>
       <c r="M965" s="3"/>
     </row>
-    <row r="966" spans="2:13">
+    <row r="966" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B966" s="2"/>
       <c r="M966" s="3"/>
     </row>
-    <row r="967" spans="2:13">
+    <row r="967" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B967" s="2"/>
       <c r="M967" s="3"/>
     </row>
-    <row r="968" spans="2:13">
+    <row r="968" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B968" s="2"/>
       <c r="M968" s="3"/>
     </row>
-    <row r="969" spans="2:13">
+    <row r="969" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B969" s="2"/>
       <c r="M969" s="3"/>
     </row>
-    <row r="970" spans="2:13">
+    <row r="970" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B970" s="2"/>
       <c r="M970" s="3"/>
     </row>
-    <row r="971" spans="2:13">
+    <row r="971" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B971" s="2"/>
       <c r="M971" s="3"/>
     </row>
-    <row r="972" spans="2:13">
+    <row r="972" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B972" s="2"/>
       <c r="M972" s="3"/>
     </row>
-    <row r="973" spans="2:13">
+    <row r="973" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B973" s="2"/>
       <c r="M973" s="3"/>
     </row>
-    <row r="974" spans="2:13">
+    <row r="974" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B974" s="2"/>
       <c r="M974" s="3"/>
     </row>
-    <row r="975" spans="2:13">
+    <row r="975" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B975" s="2"/>
       <c r="M975" s="3"/>
     </row>
-    <row r="976" spans="2:13">
+    <row r="976" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B976" s="2"/>
       <c r="M976" s="3"/>
     </row>
-    <row r="977" spans="2:13">
+    <row r="977" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B977" s="2"/>
       <c r="M977" s="3"/>
     </row>
-    <row r="978" spans="2:13">
+    <row r="978" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B978" s="2"/>
       <c r="M978" s="3"/>
     </row>
-    <row r="979" spans="2:13">
+    <row r="979" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B979" s="2"/>
       <c r="M979" s="3"/>
     </row>
-    <row r="980" spans="2:13">
+    <row r="980" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B980" s="2"/>
       <c r="M980" s="3"/>
     </row>
-    <row r="981" spans="2:13">
+    <row r="981" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B981" s="2"/>
       <c r="M981" s="3"/>
     </row>
-    <row r="982" spans="2:13">
+    <row r="982" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B982" s="2"/>
       <c r="M982" s="3"/>
     </row>
-    <row r="983" spans="2:13">
+    <row r="983" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B983" s="2"/>
       <c r="M983" s="3"/>
     </row>
-    <row r="984" spans="2:13">
+    <row r="984" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B984" s="2"/>
       <c r="M984" s="3"/>
     </row>
-    <row r="985" spans="2:13">
+    <row r="985" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B985" s="2"/>
       <c r="M985" s="3"/>
     </row>
-    <row r="986" spans="2:13">
+    <row r="986" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B986" s="2"/>
       <c r="M986" s="3"/>
     </row>
-    <row r="987" spans="2:13">
+    <row r="987" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B987" s="2"/>
       <c r="M987" s="3"/>
     </row>
-    <row r="988" spans="2:13">
+    <row r="988" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B988" s="2"/>
       <c r="M988" s="3"/>
     </row>
-    <row r="989" spans="2:13">
+    <row r="989" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B989" s="2"/>
       <c r="M989" s="3"/>
     </row>
-    <row r="990" spans="2:13">
+    <row r="990" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B990" s="2"/>
       <c r="M990" s="3"/>
     </row>
-    <row r="991" spans="2:13">
+    <row r="991" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B991" s="2"/>
       <c r="M991" s="3"/>
     </row>
-    <row r="992" spans="2:13">
+    <row r="992" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B992" s="2"/>
       <c r="M992" s="3"/>
     </row>
-    <row r="993" spans="2:13">
+    <row r="993" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B993" s="2"/>
       <c r="M993" s="3"/>
     </row>
-    <row r="994" spans="2:13">
+    <row r="994" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B994" s="2"/>
       <c r="M994" s="3"/>
     </row>
-    <row r="995" spans="2:13">
+    <row r="995" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B995" s="2"/>
       <c r="M995" s="3"/>
     </row>
-    <row r="996" spans="2:13">
+    <row r="996" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B996" s="2"/>
       <c r="M996" s="3"/>
     </row>
-    <row r="997" spans="2:13">
+    <row r="997" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B997" s="2"/>
       <c r="M997" s="3"/>
     </row>
-    <row r="998" spans="2:13">
+    <row r="998" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B998" s="2"/>
       <c r="M998" s="3"/>
     </row>
-    <row r="999" spans="2:13">
+    <row r="999" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B999" s="2"/>
       <c r="M999" s="3"/>
     </row>
-    <row r="1000" spans="2:13">
+    <row r="1000" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1000" s="2"/>
       <c r="M1000" s="3"/>
     </row>
+    <row r="1001" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1001" s="2"/>
+      <c r="M1001" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="A4:M4"/>
     <mergeCell ref="B6:M6"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="B5:M5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Select: Not Started, In Progress, or Complete" sqref="C2:J1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Select: Not Started, In Progress, or Complete" sqref="C2:J1001" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,Complete"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/Empire Carpet Care - Unit Renovation Tracker.xlsx
+++ b/data/Empire Carpet Care - Unit Renovation Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE4B51E-6969-4060-9C1E-FD9F8E585357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C28502F-4789-45E6-B380-FB7BC1E6A690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,7 +566,12 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B2" s="2"/>
+      <c r="A2">
+        <v>111</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
       <c r="M2" s="3"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">

--- a/data/Empire Carpet Care - Unit Renovation Tracker.xlsx
+++ b/data/Empire Carpet Care - Unit Renovation Tracker.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C28502F-4789-45E6-B380-FB7BC1E6A690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7DA464-AB82-432C-92F8-912E6C92DC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="RenovationTracker" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RenovationUnits">RenovationTracker!A1:M1</definedName>
+    <definedName name="RenovationUnits">'Sheet 1'!A1:M1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>

--- a/data/Empire Carpet Care - Unit Renovation Tracker.xlsx
+++ b/data/Empire Carpet Care - Unit Renovation Tracker.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7DA464-AB82-432C-92F8-912E6C92DC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2A5556-6F03-43C8-864A-FF562EF1DC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RenovationUnits">'Sheet 1'!A1:M1</definedName>
+    <definedName name="RenovationUnits">Sheet1!A1:M1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
